--- a/clustering/sepsectors/retail sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/retail sector (VDS_s) 0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="17">
   <si>
     <t>sector</t>
   </si>
@@ -68,6 +68,9 @@
   <si>
     <t>нижний кластер:</t>
   </si>
+  <si>
+    <t>разница</t>
+  </si>
 </sst>
 </file>
 
@@ -76,7 +79,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,6 +99,15 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -135,7 +147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -152,6 +164,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -455,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="93" customWidth="1"/>
@@ -773,7 +786,7 @@
         <v>4872251.3082260424</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>14</v>
       </c>
@@ -794,7 +807,7 @@
         <v>1.0257590125276369E-3</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>15</v>
       </c>
@@ -815,11 +828,833 @@
         <v>4.3731190154563726E-4</v>
       </c>
     </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1252686.154182706</v>
+      </c>
+      <c r="E22" s="4">
+        <v>9796.3168782600005</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0.13430184443805829</v>
+      </c>
+      <c r="G22" s="3">
+        <v>5.218380319387952E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1194490.274669243</v>
+      </c>
+      <c r="E23" s="4">
+        <v>19231.118310289999</v>
+      </c>
+      <c r="F23" s="3">
+        <v>5.2147019888250969E-3</v>
+      </c>
+      <c r="G23" s="3">
+        <v>4.9058279907476332E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1165717.934645507</v>
+      </c>
+      <c r="E24" s="4">
+        <v>8785.8682089999984</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1.025148686019859E-2</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1.7444704536200269E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1063712.5319653209</v>
+      </c>
+      <c r="E25" s="4">
+        <v>8180.2586681400007</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1.6866644248961379E-2</v>
+      </c>
+      <c r="G25" s="3">
+        <v>6.3103132179727491E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="4">
+        <f>AVERAGE(D22:D23)</f>
+        <v>1223588.2144259745</v>
+      </c>
+      <c r="E27" s="4">
+        <f t="shared" ref="E27:G27" si="2">AVERAGE(E22:E23)</f>
+        <v>14513.717594275</v>
+      </c>
+      <c r="F27" s="3">
+        <f t="shared" si="2"/>
+        <v>6.9758273213441691E-2</v>
+      </c>
+      <c r="G27" s="3">
+        <f t="shared" si="2"/>
+        <v>5.0621041550677926E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="4">
+        <f>AVERAGE(D24:D25)</f>
+        <v>1114715.233305414</v>
+      </c>
+      <c r="E28" s="4">
+        <f t="shared" ref="E28:G28" si="3">AVERAGE(E24:E25)</f>
+        <v>8483.0634385699996</v>
+      </c>
+      <c r="F28" s="3">
+        <f t="shared" si="3"/>
+        <v>1.3559065554579985E-2</v>
+      </c>
+      <c r="G28" s="3">
+        <f t="shared" si="3"/>
+        <v>4.0273918357963879E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="4">
+        <f>D27/D28</f>
+        <v>1.0976688735092679</v>
+      </c>
+      <c r="E30" s="4">
+        <f t="shared" ref="E30:G30" si="4">E27/E28</f>
+        <v>1.7109052289159346</v>
+      </c>
+      <c r="F30" s="4">
+        <f t="shared" si="4"/>
+        <v>5.1447699646144658</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" si="4"/>
+        <v>1.2569187110314528</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D33" s="4">
+        <v>9937990.5894197039</v>
+      </c>
+      <c r="E33" s="4">
+        <v>137654.50809200999</v>
+      </c>
+      <c r="F33" s="3">
+        <v>2.451646095414645E-3</v>
+      </c>
+      <c r="G33" s="3">
+        <v>7.6188786690442915E-4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D34" s="4">
+        <v>9153211.3096406423</v>
+      </c>
+      <c r="E34" s="4">
+        <v>158802.14720132999</v>
+      </c>
+      <c r="F34" s="3">
+        <v>2.8137256066412789E-3</v>
+      </c>
+      <c r="G34" s="3">
+        <v>2.4032687441319662E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D35" s="4">
+        <v>8323850.3002414759</v>
+      </c>
+      <c r="E35" s="4">
+        <v>69747.682037220002</v>
+      </c>
+      <c r="F35" s="3">
+        <v>3.3950559124479012E-3</v>
+      </c>
+      <c r="G35" s="3">
+        <v>9.6936097165093425E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D36" s="4">
+        <v>7695797.0900557945</v>
+      </c>
+      <c r="E36" s="4">
+        <v>86242.724574749998</v>
+      </c>
+      <c r="F36" s="3">
+        <v>2.8921735657111581E-3</v>
+      </c>
+      <c r="G36" s="3">
+        <v>1.1051378185227779E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B38" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="4">
+        <f>AVERAGE(D33:D34)</f>
+        <v>9545600.9495301731</v>
+      </c>
+      <c r="E38" s="4">
+        <f t="shared" ref="E38:G38" si="5">AVERAGE(E33:E34)</f>
+        <v>148228.32764666999</v>
+      </c>
+      <c r="F38" s="3">
+        <f t="shared" si="5"/>
+        <v>2.6326858510279617E-3</v>
+      </c>
+      <c r="G38" s="3">
+        <f t="shared" si="5"/>
+        <v>1.5825783055181976E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="4">
+        <f>AVERAGE(D35:D36)</f>
+        <v>8009823.6951486357</v>
+      </c>
+      <c r="E39" s="4">
+        <f t="shared" ref="E39:G39" si="6">AVERAGE(E35:E36)</f>
+        <v>77995.203305984993</v>
+      </c>
+      <c r="F39" s="3">
+        <f t="shared" si="6"/>
+        <v>3.1436147390795297E-3</v>
+      </c>
+      <c r="G39" s="3">
+        <f t="shared" si="6"/>
+        <v>1.0372493950868561E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="4">
+        <f>D38/D39</f>
+        <v>1.1917367114224651</v>
+      </c>
+      <c r="E41" s="4">
+        <f t="shared" ref="E41:G41" si="7">E38/E39</f>
+        <v>1.9004800470248358</v>
+      </c>
+      <c r="F41" s="4">
+        <f t="shared" si="7"/>
+        <v>0.8374708956221617</v>
+      </c>
+      <c r="G41" s="4">
+        <f t="shared" si="7"/>
+        <v>1.5257452190518532</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D44" s="4">
+        <v>5034263.5495518269</v>
+      </c>
+      <c r="E44" s="4">
+        <v>65873.429441999993</v>
+      </c>
+      <c r="F44" s="3">
+        <v>2.9423350149191101E-3</v>
+      </c>
+      <c r="G44" s="3">
+        <v>3.4897071466789652E-4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D45" s="4">
+        <v>4961117.4365704898</v>
+      </c>
+      <c r="E45" s="4">
+        <v>63209.692581750001</v>
+      </c>
+      <c r="F45" s="3">
+        <v>4.351387458407175E-3</v>
+      </c>
+      <c r="G45" s="3">
+        <v>5.6592795928781631E-4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D46" s="4">
+        <v>4783385.1798815951</v>
+      </c>
+      <c r="E46" s="4">
+        <v>64669.840333150009</v>
+      </c>
+      <c r="F46" s="3">
+        <v>2.0954023999737231E-3</v>
+      </c>
+      <c r="G46" s="3">
+        <v>5.9056880507593645E-4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D47" s="4">
+        <v>4448196.0441567702</v>
+      </c>
+      <c r="E47" s="4">
+        <v>96473.926682400008</v>
+      </c>
+      <c r="F47" s="3">
+        <v>4.425446074207404E-4</v>
+      </c>
+      <c r="G47" s="3">
+        <v>2.154034060250509E-4</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B49" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="4">
+        <f>AVERAGE(D44:D45)</f>
+        <v>4997690.4930611588</v>
+      </c>
+      <c r="E49" s="4">
+        <f t="shared" ref="E49:G49" si="8">AVERAGE(E44:E45)</f>
+        <v>64541.561011874997</v>
+      </c>
+      <c r="F49" s="3">
+        <f t="shared" si="8"/>
+        <v>3.6468612366631426E-3</v>
+      </c>
+      <c r="G49" s="3">
+        <f t="shared" si="8"/>
+        <v>4.5744933697785639E-4</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="4">
+        <f>AVERAGE(D46:D47)</f>
+        <v>4615790.6120191831</v>
+      </c>
+      <c r="E50" s="4">
+        <f t="shared" ref="E50:G50" si="9">AVERAGE(E46:E47)</f>
+        <v>80571.883507775012</v>
+      </c>
+      <c r="F50" s="3">
+        <f t="shared" si="9"/>
+        <v>1.2689735036972318E-3</v>
+      </c>
+      <c r="G50" s="3">
+        <f t="shared" si="9"/>
+        <v>4.0298610555049367E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C52" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D52" s="4">
+        <f>D49/D50</f>
+        <v>1.0827376961267559</v>
+      </c>
+      <c r="E52" s="4">
+        <f t="shared" ref="E52:G52" si="10">E49/E50</f>
+        <v>0.80104322006630113</v>
+      </c>
+      <c r="F52" s="4">
+        <f t="shared" si="10"/>
+        <v>2.8738671264906555</v>
+      </c>
+      <c r="G52" s="4">
+        <f t="shared" si="10"/>
+        <v>1.1351491544676557</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A2:G13">
-    <sortCondition descending="1" ref="D2:D13"/>
+  <sortState ref="A22:G25">
+    <sortCondition descending="1" ref="D22:D25"/>
   </sortState>
   <conditionalFormatting sqref="D2:D13">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E13">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F13">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D18">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E18">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F18">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17:G18">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:D25">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E22:E25">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F25">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:G25">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D27:D28">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E27:E28">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27:F28">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27:G28">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D33:D36">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E33:E36">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33:F36">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G33:G36">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D38:D39">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E38:E39">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F38:F39">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G38:G39">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D44:D47">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -831,7 +1666,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
+  <conditionalFormatting sqref="E44:E47">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -843,7 +1678,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
+  <conditionalFormatting sqref="F44:F47">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -855,7 +1690,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
+  <conditionalFormatting sqref="G44:G47">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -867,7 +1702,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D17:D18">
+  <conditionalFormatting sqref="D49:D50">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -879,7 +1714,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E17:E18">
+  <conditionalFormatting sqref="E49:E50">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -891,7 +1726,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17:F18">
+  <conditionalFormatting sqref="F49:F50">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -903,7 +1738,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
+  <conditionalFormatting sqref="G49:G50">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/clustering/sepsectors/retail sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/retail sector (VDS_s) 0.xlsx
@@ -14,12 +14,15 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="18">
   <si>
     <t>sector</t>
   </si>
@@ -70,6 +73,9 @@
   </si>
   <si>
     <t>разница</t>
+  </si>
+  <si>
+    <t>Year</t>
   </si>
 </sst>
 </file>
@@ -147,7 +153,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -165,6 +171,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -181,6 +190,3072 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>45</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,85</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$40:$G$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.42536572944710072</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.12558758459002764</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2271-4755-BA51-C1DB21D4CD23}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$43</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$43:$G$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.50939923098586959</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.82696058644524917</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-2271-4755-BA51-C1DB21D4CD23}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>46</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$65</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,77</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$65:$G$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.54308286187976496</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.85187803685561247</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.4598477890669449</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8757-4C2A-B4AA-DFB826FDC685}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$68</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$68:$G$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.86683026972860167</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.72212245059815838</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.31702150197089779</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-8757-4C2A-B4AA-DFB826FDC685}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>47</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$90</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,88</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$90:$G$90</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10170195406656198</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.36473888253774922</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0CEA-4588-9C3E-F6A565202494}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$93</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$93:$G$93</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.68281070033420188</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.67618318135157551</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.59090610893852613</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-0CEA-4588-9C3E-F6A565202494}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>176893</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>579387</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>122172</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>122464</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>89531</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>135779</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>27214</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>606602</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>81351</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Original"/>
+      <sheetName val="Only best"/>
+      <sheetName val="Best|Worst"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="89">
+          <cell r="D89" t="str">
+            <v>Year</v>
+          </cell>
+          <cell r="E89" t="str">
+            <v>ITcosts_s</v>
+          </cell>
+          <cell r="F89" t="str">
+            <v>skvozcosts_s</v>
+          </cell>
+          <cell r="G89" t="str">
+            <v>trainingcosts_s</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="C90">
+            <v>0.60541707637600206</v>
+          </cell>
+          <cell r="D90">
+            <v>0.75</v>
+          </cell>
+          <cell r="E90">
+            <v>1</v>
+          </cell>
+          <cell r="F90">
+            <v>0.80661939562538798</v>
+          </cell>
+          <cell r="G90">
+            <v>0.45477225885659545</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="C91">
+            <v>0.62826451624711255</v>
+          </cell>
+          <cell r="D91">
+            <v>1</v>
+          </cell>
+          <cell r="E91">
+            <v>0.7323973572762863</v>
+          </cell>
+          <cell r="F91">
+            <v>0.9611546957323327</v>
+          </cell>
+          <cell r="G91">
+            <v>0.83771179639168136</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0.78924387345553881</v>
+          </cell>
+          <cell r="D92">
+            <v>0.5</v>
+          </cell>
+          <cell r="E92">
+            <v>0.90624842311195075</v>
+          </cell>
+          <cell r="F92">
+            <v>1</v>
+          </cell>
+          <cell r="G92">
+            <v>0.67809276193519175</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="C93">
+            <v>1</v>
+          </cell>
+          <cell r="D93">
+            <v>0.25</v>
+          </cell>
+          <cell r="E93">
+            <v>0.89882061387652312</v>
+          </cell>
+          <cell r="F93">
+            <v>0.17795127025264079</v>
+          </cell>
+          <cell r="G93">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -468,7 +3543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="93" customWidth="1"/>
@@ -859,7 +3934,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="2">
-        <v>2023</v>
+        <v>3</v>
       </c>
       <c r="D22" s="4">
         <v>1252686.154182706</v>
@@ -882,7 +3957,7 @@
         <v>8</v>
       </c>
       <c r="C23" s="2">
-        <v>2021</v>
+        <v>1</v>
       </c>
       <c r="D23" s="4">
         <v>1194490.274669243</v>
@@ -905,7 +3980,7 @@
         <v>8</v>
       </c>
       <c r="C24" s="2">
-        <v>2024</v>
+        <v>4</v>
       </c>
       <c r="D24" s="4">
         <v>1165717.934645507</v>
@@ -928,7 +4003,7 @@
         <v>8</v>
       </c>
       <c r="C25" s="2">
-        <v>2022</v>
+        <v>2</v>
       </c>
       <c r="D25" s="4">
         <v>1063712.5319653209</v>
@@ -1007,364 +4082,1000 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="C32" s="2">
+        <f>MAX(C22:C25)</f>
+        <v>4</v>
+      </c>
+      <c r="D32" s="2">
+        <f t="shared" ref="D32:G32" si="5">MAX(D22:D25)</f>
+        <v>1252686.154182706</v>
+      </c>
+      <c r="E32" s="2">
+        <f t="shared" si="5"/>
+        <v>19231.118310289999</v>
+      </c>
+      <c r="F32" s="2">
+        <f t="shared" si="5"/>
+        <v>0.13430184443805829</v>
+      </c>
+      <c r="G32" s="2">
+        <f t="shared" si="5"/>
+        <v>6.3103132179727491E-4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C34" s="2">
+        <f>C22/C$32</f>
+        <v>0.75</v>
+      </c>
+      <c r="D34" s="2">
+        <f t="shared" ref="D34:G34" si="6">D22/D$32</f>
+        <v>1</v>
+      </c>
+      <c r="E34" s="2">
+        <f t="shared" si="6"/>
+        <v>0.50939923098586959</v>
+      </c>
+      <c r="F34" s="2">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="G34" s="2">
+        <f t="shared" si="6"/>
+        <v>0.82696058644524917</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C35" s="2">
+        <f t="shared" ref="C35:G37" si="7">C23/C$32</f>
+        <v>0.25</v>
+      </c>
+      <c r="D35" s="2">
+        <f t="shared" si="7"/>
+        <v>0.95354312864467483</v>
+      </c>
+      <c r="E35" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <f t="shared" si="7"/>
+        <v>3.882822317626608E-2</v>
+      </c>
+      <c r="G35" s="2">
+        <f t="shared" si="7"/>
+        <v>0.7774301878986094</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C36" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="D36" s="2">
+        <f t="shared" si="7"/>
+        <v>0.93057461420259735</v>
+      </c>
+      <c r="E36" s="2">
+        <f t="shared" si="7"/>
+        <v>0.45685685394067499</v>
+      </c>
+      <c r="F36" s="2">
+        <f t="shared" si="7"/>
+        <v>7.6331690775302094E-2</v>
+      </c>
+      <c r="G36" s="2">
+        <f t="shared" si="7"/>
+        <v>0.27644752223257396</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.5</v>
+      </c>
+      <c r="D37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.84914527746123469</v>
+      </c>
+      <c r="E37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.42536572944710072</v>
+      </c>
+      <c r="F37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.12558758459002764</v>
+      </c>
+      <c r="G37" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C39" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C40" s="4">
+        <v>0.84914527746123469</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.42536572944710072</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0.12558758459002764</v>
+      </c>
+      <c r="G40" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C41" s="4">
+        <v>0.93057461420259735</v>
+      </c>
+      <c r="D41" s="2">
+        <v>1</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.45685685394067499</v>
+      </c>
+      <c r="F41" s="2">
+        <v>7.6331690775302094E-2</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0.27644752223257396</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C42" s="4">
+        <v>0.95354312864467483</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E42" s="2">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>3.882822317626608E-2</v>
+      </c>
+      <c r="G42" s="2">
+        <v>0.7774301878986094</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C43" s="4">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0.50939923098586959</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.82696058644524917</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E46" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D33" s="4">
-        <v>9937990.5894197039</v>
-      </c>
-      <c r="E33" s="4">
-        <v>137654.50809200999</v>
-      </c>
-      <c r="F33" s="3">
-        <v>2.451646095414645E-3</v>
-      </c>
-      <c r="G33" s="3">
-        <v>7.6188786690442915E-4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D34" s="4">
-        <v>9153211.3096406423</v>
-      </c>
-      <c r="E34" s="4">
-        <v>158802.14720132999</v>
-      </c>
-      <c r="F34" s="3">
-        <v>2.8137256066412789E-3</v>
-      </c>
-      <c r="G34" s="3">
-        <v>2.4032687441319662E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D35" s="4">
-        <v>8323850.3002414759</v>
-      </c>
-      <c r="E35" s="4">
-        <v>69747.682037220002</v>
-      </c>
-      <c r="F35" s="3">
-        <v>3.3950559124479012E-3</v>
-      </c>
-      <c r="G35" s="3">
-        <v>9.6936097165093425E-4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D36" s="4">
-        <v>7695797.0900557945</v>
-      </c>
-      <c r="E36" s="4">
-        <v>86242.724574749998</v>
-      </c>
-      <c r="F36" s="3">
-        <v>2.8921735657111581E-3</v>
-      </c>
-      <c r="G36" s="3">
-        <v>1.1051378185227779E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B38" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D38" s="4">
-        <f>AVERAGE(D33:D34)</f>
-        <v>9545600.9495301731</v>
-      </c>
-      <c r="E38" s="4">
-        <f t="shared" ref="E38:G38" si="5">AVERAGE(E33:E34)</f>
-        <v>148228.32764666999</v>
-      </c>
-      <c r="F38" s="3">
-        <f t="shared" si="5"/>
-        <v>2.6326858510279617E-3</v>
-      </c>
-      <c r="G38" s="3">
-        <f t="shared" si="5"/>
-        <v>1.5825783055181976E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" s="4">
-        <f>AVERAGE(D35:D36)</f>
-        <v>8009823.6951486357</v>
-      </c>
-      <c r="E39" s="4">
-        <f t="shared" ref="E39:G39" si="6">AVERAGE(E35:E36)</f>
-        <v>77995.203305984993</v>
-      </c>
-      <c r="F39" s="3">
-        <f t="shared" si="6"/>
-        <v>3.1436147390795297E-3</v>
-      </c>
-      <c r="G39" s="3">
-        <f t="shared" si="6"/>
-        <v>1.0372493950868561E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C41" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D41" s="4">
-        <f>D38/D39</f>
-        <v>1.1917367114224651</v>
-      </c>
-      <c r="E41" s="4">
-        <f t="shared" ref="E41:G41" si="7">E38/E39</f>
-        <v>1.9004800470248358</v>
-      </c>
-      <c r="F41" s="4">
-        <f t="shared" si="7"/>
-        <v>0.8374708956221617</v>
-      </c>
-      <c r="G41" s="4">
-        <f t="shared" si="7"/>
-        <v>1.5257452190518532</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D44" s="4">
-        <v>5034263.5495518269</v>
-      </c>
-      <c r="E44" s="4">
-        <v>65873.429441999993</v>
-      </c>
-      <c r="F44" s="3">
-        <v>2.9423350149191101E-3</v>
-      </c>
-      <c r="G44" s="3">
-        <v>3.4897071466789652E-4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D45" s="4">
-        <v>4961117.4365704898</v>
-      </c>
-      <c r="E45" s="4">
-        <v>63209.692581750001</v>
-      </c>
-      <c r="F45" s="3">
-        <v>4.351387458407175E-3</v>
-      </c>
-      <c r="G45" s="3">
-        <v>5.6592795928781631E-4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D46" s="4">
-        <v>4783385.1798815951</v>
-      </c>
-      <c r="E46" s="4">
-        <v>64669.840333150009</v>
-      </c>
-      <c r="F46" s="3">
-        <v>2.0954023999737231E-3</v>
-      </c>
-      <c r="G46" s="3">
-        <v>5.9056880507593645E-4</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="2">
+        <v>2</v>
+      </c>
+      <c r="D47" s="4">
+        <v>9937990.5894197039</v>
+      </c>
+      <c r="E47" s="4">
+        <v>137654.50809200999</v>
+      </c>
+      <c r="F47" s="3">
+        <v>2.451646095414645E-3</v>
+      </c>
+      <c r="G47" s="3">
+        <v>7.6188786690442915E-4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1</v>
+      </c>
+      <c r="D48" s="4">
+        <v>9153211.3096406423</v>
+      </c>
+      <c r="E48" s="4">
+        <v>158802.14720132999</v>
+      </c>
+      <c r="F48" s="3">
+        <v>2.8137256066412789E-3</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2.4032687441319662E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="2">
+        <v>3</v>
+      </c>
+      <c r="D49" s="4">
+        <v>8323850.3002414759</v>
+      </c>
+      <c r="E49" s="4">
+        <v>69747.682037220002</v>
+      </c>
+      <c r="F49" s="3">
+        <v>3.3950559124479012E-3</v>
+      </c>
+      <c r="G49" s="3">
+        <v>9.6936097165093425E-4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="2">
+        <v>4</v>
+      </c>
+      <c r="D50" s="4">
+        <v>7695797.0900557945</v>
+      </c>
+      <c r="E50" s="4">
+        <v>86242.724574749998</v>
+      </c>
+      <c r="F50" s="3">
+        <v>2.8921735657111581E-3</v>
+      </c>
+      <c r="G50" s="3">
+        <v>1.1051378185227779E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="4">
+        <f>AVERAGE(D47:D48)</f>
+        <v>9545600.9495301731</v>
+      </c>
+      <c r="E52" s="4">
+        <f t="shared" ref="E52:G52" si="8">AVERAGE(E47:E48)</f>
+        <v>148228.32764666999</v>
+      </c>
+      <c r="F52" s="3">
+        <f t="shared" si="8"/>
+        <v>2.6326858510279617E-3</v>
+      </c>
+      <c r="G52" s="3">
+        <f t="shared" si="8"/>
+        <v>1.5825783055181976E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="4">
+        <f>AVERAGE(D49:D50)</f>
+        <v>8009823.6951486357</v>
+      </c>
+      <c r="E53" s="4">
+        <f t="shared" ref="E53:G53" si="9">AVERAGE(E49:E50)</f>
+        <v>77995.203305984993</v>
+      </c>
+      <c r="F53" s="3">
+        <f t="shared" si="9"/>
+        <v>3.1436147390795297E-3</v>
+      </c>
+      <c r="G53" s="3">
+        <f t="shared" si="9"/>
+        <v>1.0372493950868561E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C55" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="4">
+        <f>D52/D53</f>
+        <v>1.1917367114224651</v>
+      </c>
+      <c r="E55" s="4">
+        <f t="shared" ref="E55:G55" si="10">E52/E53</f>
+        <v>1.9004800470248358</v>
+      </c>
+      <c r="F55" s="4">
+        <f t="shared" si="10"/>
+        <v>0.8374708956221617</v>
+      </c>
+      <c r="G55" s="4">
+        <f t="shared" si="10"/>
+        <v>1.5257452190518532</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C57" s="2">
+        <f>MAX(C47:C50)</f>
+        <v>4</v>
+      </c>
+      <c r="D57" s="2">
+        <f t="shared" ref="D57:G57" si="11">MAX(D47:D50)</f>
+        <v>9937990.5894197039</v>
+      </c>
+      <c r="E57" s="2">
+        <f t="shared" si="11"/>
+        <v>158802.14720132999</v>
+      </c>
+      <c r="F57" s="2">
+        <f t="shared" si="11"/>
+        <v>3.3950559124479012E-3</v>
+      </c>
+      <c r="G57" s="2">
+        <f t="shared" si="11"/>
+        <v>2.4032687441319662E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C59" s="2">
+        <f>C47/C$57</f>
+        <v>0.5</v>
+      </c>
+      <c r="D59" s="2">
+        <f t="shared" ref="D59:G59" si="12">D47/D$57</f>
+        <v>1</v>
+      </c>
+      <c r="E59" s="2">
+        <f t="shared" si="12"/>
+        <v>0.86683026972860167</v>
+      </c>
+      <c r="F59" s="2">
+        <f t="shared" si="12"/>
+        <v>0.72212245059815838</v>
+      </c>
+      <c r="G59" s="2">
+        <f t="shared" si="12"/>
+        <v>0.31702150197089779</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C60" s="2">
+        <f t="shared" ref="C60:G62" si="13">C48/C$57</f>
+        <v>0.25</v>
+      </c>
+      <c r="D60" s="2">
+        <f t="shared" si="13"/>
+        <v>0.9210323985801957</v>
+      </c>
+      <c r="E60" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="F60" s="2">
+        <f t="shared" si="13"/>
+        <v>0.82877150751032203</v>
+      </c>
+      <c r="G60" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C61" s="2">
+        <f t="shared" si="13"/>
+        <v>0.75</v>
+      </c>
+      <c r="D61" s="2">
+        <f t="shared" si="13"/>
+        <v>0.83757880683679731</v>
+      </c>
+      <c r="E61" s="2">
+        <f t="shared" si="13"/>
+        <v>0.43921120253363838</v>
+      </c>
+      <c r="F61" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="G61" s="2">
+        <f t="shared" si="13"/>
+        <v>0.40335105011364702</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C62" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="D62" s="2">
+        <f t="shared" si="13"/>
+        <v>0.77438160368646158</v>
+      </c>
+      <c r="E62" s="2">
+        <f t="shared" si="13"/>
+        <v>0.54308286187976496</v>
+      </c>
+      <c r="F62" s="2">
+        <f t="shared" si="13"/>
+        <v>0.85187803685561247</v>
+      </c>
+      <c r="G62" s="2">
+        <f t="shared" si="13"/>
+        <v>0.4598477890669449</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C64" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C65" s="4">
+        <v>0.77438160368646158</v>
+      </c>
+      <c r="D65" s="2">
+        <v>1</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0.54308286187976496</v>
+      </c>
+      <c r="F65" s="2">
+        <v>0.85187803685561247</v>
+      </c>
+      <c r="G65" s="2">
+        <v>0.4598477890669449</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C66" s="4">
+        <v>0.83757880683679731</v>
+      </c>
+      <c r="D66" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0.43921120253363838</v>
+      </c>
+      <c r="F66" s="2">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2">
+        <v>0.40335105011364702</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C67" s="4">
+        <v>0.9210323985801957</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E67" s="2">
+        <v>1</v>
+      </c>
+      <c r="F67" s="2">
+        <v>0.82877150751032203</v>
+      </c>
+      <c r="G67" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C68" s="4">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0.86683026972860167</v>
+      </c>
+      <c r="F68" s="2">
+        <v>0.72212245059815838</v>
+      </c>
+      <c r="G68" s="2">
+        <v>0.31702150197089779</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B72" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C47" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D47" s="4">
+      <c r="C72" s="2">
+        <v>4</v>
+      </c>
+      <c r="D72" s="4">
+        <v>5034263.5495518269</v>
+      </c>
+      <c r="E72" s="4">
+        <v>65873.429441999993</v>
+      </c>
+      <c r="F72" s="3">
+        <v>2.9423350149191101E-3</v>
+      </c>
+      <c r="G72" s="3">
+        <v>3.4897071466789652E-4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="2">
+        <v>3</v>
+      </c>
+      <c r="D73" s="4">
+        <v>4961117.4365704898</v>
+      </c>
+      <c r="E73" s="4">
+        <v>63209.692581750001</v>
+      </c>
+      <c r="F73" s="3">
+        <v>4.351387458407175E-3</v>
+      </c>
+      <c r="G73" s="3">
+        <v>5.6592795928781631E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" s="2">
+        <v>2</v>
+      </c>
+      <c r="D74" s="4">
+        <v>4783385.1798815951</v>
+      </c>
+      <c r="E74" s="4">
+        <v>64669.840333150009</v>
+      </c>
+      <c r="F74" s="3">
+        <v>2.0954023999737231E-3</v>
+      </c>
+      <c r="G74" s="3">
+        <v>5.9056880507593645E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="2">
+        <v>1</v>
+      </c>
+      <c r="D75" s="4">
         <v>4448196.0441567702</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E75" s="4">
         <v>96473.926682400008</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F75" s="3">
         <v>4.425446074207404E-4</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G75" s="3">
         <v>2.154034060250509E-4</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="6" t="s">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B77" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D49" s="4">
-        <f>AVERAGE(D44:D45)</f>
+      <c r="D77" s="4">
+        <f>AVERAGE(D72:D73)</f>
         <v>4997690.4930611588</v>
       </c>
-      <c r="E49" s="4">
-        <f t="shared" ref="E49:G49" si="8">AVERAGE(E44:E45)</f>
+      <c r="E77" s="4">
+        <f t="shared" ref="E77:G77" si="14">AVERAGE(E72:E73)</f>
         <v>64541.561011874997</v>
       </c>
-      <c r="F49" s="3">
-        <f t="shared" si="8"/>
+      <c r="F77" s="3">
+        <f t="shared" si="14"/>
         <v>3.6468612366631426E-3</v>
       </c>
-      <c r="G49" s="3">
-        <f t="shared" si="8"/>
+      <c r="G77" s="3">
+        <f t="shared" si="14"/>
         <v>4.5744933697785639E-4</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B50" s="6" t="s">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D50" s="4">
-        <f>AVERAGE(D46:D47)</f>
+      <c r="D78" s="4">
+        <f>AVERAGE(D74:D75)</f>
         <v>4615790.6120191831</v>
       </c>
-      <c r="E50" s="4">
-        <f t="shared" ref="E50:G50" si="9">AVERAGE(E46:E47)</f>
+      <c r="E78" s="4">
+        <f t="shared" ref="E78:G78" si="15">AVERAGE(E74:E75)</f>
         <v>80571.883507775012</v>
       </c>
-      <c r="F50" s="3">
-        <f t="shared" si="9"/>
+      <c r="F78" s="3">
+        <f t="shared" si="15"/>
         <v>1.2689735036972318E-3</v>
       </c>
-      <c r="G50" s="3">
-        <f t="shared" si="9"/>
+      <c r="G78" s="3">
+        <f t="shared" si="15"/>
         <v>4.0298610555049367E-4</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C52" s="6" t="s">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C80" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D52" s="4">
-        <f>D49/D50</f>
+      <c r="D80" s="4">
+        <f>D77/D78</f>
         <v>1.0827376961267559</v>
       </c>
-      <c r="E52" s="4">
-        <f t="shared" ref="E52:G52" si="10">E49/E50</f>
+      <c r="E80" s="4">
+        <f t="shared" ref="E80:G80" si="16">E77/E78</f>
         <v>0.80104322006630113</v>
       </c>
-      <c r="F52" s="4">
-        <f t="shared" si="10"/>
+      <c r="F80" s="4">
+        <f t="shared" si="16"/>
         <v>2.8738671264906555</v>
       </c>
-      <c r="G52" s="4">
-        <f t="shared" si="10"/>
+      <c r="G80" s="4">
+        <f t="shared" si="16"/>
         <v>1.1351491544676557</v>
       </c>
     </row>
+    <row r="82" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C82" s="2">
+        <f>MAX(C72:C75)</f>
+        <v>4</v>
+      </c>
+      <c r="D82" s="2">
+        <f t="shared" ref="D82:G82" si="17">MAX(D72:D75)</f>
+        <v>5034263.5495518269</v>
+      </c>
+      <c r="E82" s="2">
+        <f t="shared" si="17"/>
+        <v>96473.926682400008</v>
+      </c>
+      <c r="F82" s="2">
+        <f t="shared" si="17"/>
+        <v>4.351387458407175E-3</v>
+      </c>
+      <c r="G82" s="2">
+        <f t="shared" si="17"/>
+        <v>5.9056880507593645E-4</v>
+      </c>
+    </row>
+    <row r="83" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C83" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C84" s="2">
+        <f>C72/C$82</f>
+        <v>1</v>
+      </c>
+      <c r="D84" s="2">
+        <f t="shared" ref="D84:G84" si="18">D72/D$82</f>
+        <v>1</v>
+      </c>
+      <c r="E84" s="2">
+        <f t="shared" si="18"/>
+        <v>0.68281070033420188</v>
+      </c>
+      <c r="F84" s="2">
+        <f t="shared" si="18"/>
+        <v>0.67618318135157551</v>
+      </c>
+      <c r="G84" s="2">
+        <f t="shared" si="18"/>
+        <v>0.59090610893852613</v>
+      </c>
+    </row>
+    <row r="85" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C85" s="2">
+        <f t="shared" ref="C85:G87" si="19">C73/C$82</f>
+        <v>0.75</v>
+      </c>
+      <c r="D85" s="2">
+        <f t="shared" si="19"/>
+        <v>0.98547034491512686</v>
+      </c>
+      <c r="E85" s="2">
+        <f t="shared" si="19"/>
+        <v>0.65519974935654313</v>
+      </c>
+      <c r="F85" s="2">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="G85" s="2">
+        <f t="shared" si="19"/>
+        <v>0.95827607964333339</v>
+      </c>
+    </row>
+    <row r="86" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C86" s="2">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="D86" s="2">
+        <f t="shared" si="19"/>
+        <v>0.95016582520941595</v>
+      </c>
+      <c r="E86" s="2">
+        <f t="shared" si="19"/>
+        <v>0.67033490350245994</v>
+      </c>
+      <c r="F86" s="2">
+        <f t="shared" si="19"/>
+        <v>0.48154810850623375</v>
+      </c>
+      <c r="G86" s="2">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C87" s="2">
+        <f t="shared" si="19"/>
+        <v>0.25</v>
+      </c>
+      <c r="D87" s="2">
+        <f t="shared" si="19"/>
+        <v>0.88358426220112551</v>
+      </c>
+      <c r="E87" s="2">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="F87" s="2">
+        <f t="shared" si="19"/>
+        <v>0.10170195406656198</v>
+      </c>
+      <c r="G87" s="2">
+        <f t="shared" si="19"/>
+        <v>0.36473888253774922</v>
+      </c>
+    </row>
+    <row r="89" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C89" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C90" s="4">
+        <v>0.88358426220112551</v>
+      </c>
+      <c r="D90" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E90" s="2">
+        <v>1</v>
+      </c>
+      <c r="F90" s="2">
+        <v>0.10170195406656198</v>
+      </c>
+      <c r="G90" s="2">
+        <v>0.36473888253774922</v>
+      </c>
+    </row>
+    <row r="91" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C91" s="4">
+        <v>0.95016582520941595</v>
+      </c>
+      <c r="D91" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E91" s="2">
+        <v>0.67033490350245994</v>
+      </c>
+      <c r="F91" s="2">
+        <v>0.48154810850623375</v>
+      </c>
+      <c r="G91" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C92" s="4">
+        <v>0.98547034491512686</v>
+      </c>
+      <c r="D92" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0.65519974935654313</v>
+      </c>
+      <c r="F92" s="2">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2">
+        <v>0.95827607964333339</v>
+      </c>
+    </row>
+    <row r="93" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C93" s="4">
+        <v>1</v>
+      </c>
+      <c r="D93" s="2">
+        <v>1</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0.68281070033420188</v>
+      </c>
+      <c r="F93" s="2">
+        <v>0.67618318135157551</v>
+      </c>
+      <c r="G93" s="2">
+        <v>0.59090610893852613</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A22:G25">
-    <sortCondition descending="1" ref="D22:D25"/>
+  <sortState ref="C90:G93">
+    <sortCondition ref="C90:C93"/>
   </sortState>
   <conditionalFormatting sqref="D2:D13">
     <cfRule type="colorScale" priority="32">
@@ -1558,7 +5269,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D33:D36">
+  <conditionalFormatting sqref="D47:D50">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -1570,7 +5281,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E33:E36">
+  <conditionalFormatting sqref="E47:E50">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -1582,7 +5293,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33:F36">
+  <conditionalFormatting sqref="F47:F50">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -1594,7 +5305,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G33:G36">
+  <conditionalFormatting sqref="G47:G50">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -1606,7 +5317,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D38:D39">
+  <conditionalFormatting sqref="D52:D53">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -1618,7 +5329,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E38:E39">
+  <conditionalFormatting sqref="E52:E53">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -1630,7 +5341,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F38:F39">
+  <conditionalFormatting sqref="F52:F53">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -1642,7 +5353,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G38:G39">
+  <conditionalFormatting sqref="G52:G53">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -1654,7 +5365,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D44:D47">
+  <conditionalFormatting sqref="D72:D75">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -1666,7 +5377,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E44:E47">
+  <conditionalFormatting sqref="E72:E75">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -1678,7 +5389,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F44:F47">
+  <conditionalFormatting sqref="F72:F75">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -1690,7 +5401,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G44:G47">
+  <conditionalFormatting sqref="G72:G75">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1702,7 +5413,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D49:D50">
+  <conditionalFormatting sqref="D77:D78">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1714,7 +5425,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E49:E50">
+  <conditionalFormatting sqref="E77:E78">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1726,7 +5437,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F49:F50">
+  <conditionalFormatting sqref="F77:F78">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1738,7 +5449,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G49:G50">
+  <conditionalFormatting sqref="G77:G78">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1751,5 +5462,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/clustering/sepsectors/retail sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/retail sector (VDS_s) 0.xlsx
@@ -14,15 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="21">
   <si>
     <t>sector</t>
   </si>
@@ -76,6 +73,15 @@
   </si>
   <si>
     <t>Year</t>
+  </si>
+  <si>
+    <t>best</t>
+  </si>
+  <si>
+    <t>worst</t>
+  </si>
+  <si>
+    <t>сред</t>
   </si>
 </sst>
 </file>
@@ -153,7 +159,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -172,6 +178,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -685,7 +694,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$65</c:f>
+              <c:f>Sheet1!$C$64</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -728,7 +737,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$65:$G$65</c:f>
+              <c:f>Sheet1!$D$64:$G$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -758,7 +767,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$68</c:f>
+              <c:f>Sheet1!$C$67</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -801,7 +810,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$68:$G$68</c:f>
+              <c:f>Sheet1!$D$67:$G$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1095,7 +1104,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$90</c:f>
+              <c:f>Sheet1!$C$88</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1138,7 +1147,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$90:$G$90</c:f>
+              <c:f>Sheet1!$D$88:$G$88</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1168,7 +1177,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$93</c:f>
+              <c:f>Sheet1!$C$91</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1211,7 +1220,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$93:$G$93</c:f>
+              <c:f>Sheet1!$D$91:$G$91</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3061,16 +3070,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>-1</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>176893</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>329044</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>38348</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>579387</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>302296</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>122172</xdr:rowOff>
+      <xdr:rowOff>174127</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3093,14 +3102,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>122464</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>434191</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>89531</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>401258</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>135779</xdr:rowOff>
     </xdr:to>
@@ -3125,16 +3134,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>27214</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>564077</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>136072</xdr:rowOff>
+      <xdr:rowOff>153390</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>606602</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>537329</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>81351</xdr:rowOff>
+      <xdr:rowOff>98669</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3156,106 +3165,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Original"/>
-      <sheetName val="Only best"/>
-      <sheetName val="Best|Worst"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="89">
-          <cell r="D89" t="str">
-            <v>Year</v>
-          </cell>
-          <cell r="E89" t="str">
-            <v>ITcosts_s</v>
-          </cell>
-          <cell r="F89" t="str">
-            <v>skvozcosts_s</v>
-          </cell>
-          <cell r="G89" t="str">
-            <v>trainingcosts_s</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="C90">
-            <v>0.60541707637600206</v>
-          </cell>
-          <cell r="D90">
-            <v>0.75</v>
-          </cell>
-          <cell r="E90">
-            <v>1</v>
-          </cell>
-          <cell r="F90">
-            <v>0.80661939562538798</v>
-          </cell>
-          <cell r="G90">
-            <v>0.45477225885659545</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="C91">
-            <v>0.62826451624711255</v>
-          </cell>
-          <cell r="D91">
-            <v>1</v>
-          </cell>
-          <cell r="E91">
-            <v>0.7323973572762863</v>
-          </cell>
-          <cell r="F91">
-            <v>0.9611546957323327</v>
-          </cell>
-          <cell r="G91">
-            <v>0.83771179639168136</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="C92">
-            <v>0.78924387345553881</v>
-          </cell>
-          <cell r="D92">
-            <v>0.5</v>
-          </cell>
-          <cell r="E92">
-            <v>0.90624842311195075</v>
-          </cell>
-          <cell r="F92">
-            <v>1</v>
-          </cell>
-          <cell r="G92">
-            <v>0.67809276193519175</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="C93">
-            <v>1</v>
-          </cell>
-          <cell r="D93">
-            <v>0.25</v>
-          </cell>
-          <cell r="E93">
-            <v>0.89882061387652312</v>
-          </cell>
-          <cell r="F93">
-            <v>0.17795127025264079</v>
-          </cell>
-          <cell r="G93">
-            <v>1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3543,7 +3452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="93" customWidth="1"/>
@@ -3861,7 +3770,7 @@
         <v>4872251.3082260424</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>14</v>
       </c>
@@ -3882,7 +3791,7 @@
         <v>1.0257590125276369E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>15</v>
       </c>
@@ -3903,7 +3812,7 @@
         <v>4.3731190154563726E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
@@ -3925,8 +3834,15 @@
       <c r="G21" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I21" s="2"/>
+      <c r="J21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
@@ -3948,8 +3864,17 @@
       <c r="G22" s="3">
         <v>5.218380319387952E-4</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I22" s="7">
+        <v>45</v>
+      </c>
+      <c r="J22" s="4">
+        <v>1.1693148402522289</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0.44584555192110731</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>7</v>
       </c>
@@ -3971,8 +3896,17 @@
       <c r="G23" s="3">
         <v>4.9058279907476332E-4</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I23" s="7">
+        <v>46</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0.72340591418718192</v>
+      </c>
+      <c r="K23" s="4">
+        <v>0.92865262248875724</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
@@ -3994,8 +3928,17 @@
       <c r="G24" s="3">
         <v>1.7444704536200269E-4</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I24" s="7">
+        <v>47</v>
+      </c>
+      <c r="J24" s="4">
+        <v>1.0674913467538696</v>
+      </c>
+      <c r="K24" s="4">
+        <v>0.2399906658895713</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
@@ -4017,8 +3960,22 @@
       <c r="G25" s="3">
         <v>6.3103132179727491E-4</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I25" s="6"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I26" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="8">
+        <f>AVERAGE(J22:J24)</f>
+        <v>0.98673736706442672</v>
+      </c>
+      <c r="K26" s="8">
+        <f>AVERAGE(K22:K24)</f>
+        <v>0.53816294676647869</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
@@ -4038,8 +3995,9 @@
         <f t="shared" si="2"/>
         <v>5.0621041550677926E-4</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I27" s="6"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>15</v>
       </c>
@@ -4059,8 +4017,9 @@
         <f t="shared" si="3"/>
         <v>4.0273918357963879E-4</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I28" s="6"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C30" s="6" t="s">
         <v>16</v>
       </c>
@@ -4081,7 +4040,7 @@
         <v>1.2569187110314528</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C32" s="2">
         <f>MAX(C22:C25)</f>
         <v>4</v>
@@ -4293,27 +4252,50 @@
         <v>0.82696058644524917</v>
       </c>
     </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" s="1" t="s">
+      <c r="A46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="2">
         <v>2</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>6</v>
+      <c r="D46" s="4">
+        <v>9937990.5894197039</v>
+      </c>
+      <c r="E46" s="4">
+        <v>137654.50809200999</v>
+      </c>
+      <c r="F46" s="3">
+        <v>2.451646095414645E-3</v>
+      </c>
+      <c r="G46" s="3">
+        <v>7.6188786690442915E-4</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -4324,19 +4306,19 @@
         <v>10</v>
       </c>
       <c r="C47" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" s="4">
-        <v>9937990.5894197039</v>
+        <v>9153211.3096406423</v>
       </c>
       <c r="E47" s="4">
-        <v>137654.50809200999</v>
+        <v>158802.14720132999</v>
       </c>
       <c r="F47" s="3">
-        <v>2.451646095414645E-3</v>
+        <v>2.8137256066412789E-3</v>
       </c>
       <c r="G47" s="3">
-        <v>7.6188786690442915E-4</v>
+        <v>2.4032687441319662E-3</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -4347,22 +4329,22 @@
         <v>10</v>
       </c>
       <c r="C48" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D48" s="4">
-        <v>9153211.3096406423</v>
+        <v>8323850.3002414759</v>
       </c>
       <c r="E48" s="4">
-        <v>158802.14720132999</v>
+        <v>69747.682037220002</v>
       </c>
       <c r="F48" s="3">
-        <v>2.8137256066412789E-3</v>
+        <v>3.3950559124479012E-3</v>
       </c>
       <c r="G48" s="3">
-        <v>2.4032687441319662E-3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9.6936097165093425E-4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>9</v>
       </c>
@@ -4370,340 +4352,381 @@
         <v>10</v>
       </c>
       <c r="C49" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49" s="4">
-        <v>8323850.3002414759</v>
+        <v>7695797.0900557945</v>
       </c>
       <c r="E49" s="4">
-        <v>69747.682037220002</v>
+        <v>86242.724574749998</v>
       </c>
       <c r="F49" s="3">
-        <v>3.3950559124479012E-3</v>
+        <v>2.8921735657111581E-3</v>
       </c>
       <c r="G49" s="3">
-        <v>9.6936097165093425E-4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="2">
-        <v>4</v>
-      </c>
-      <c r="D50" s="4">
-        <v>7695797.0900557945</v>
-      </c>
-      <c r="E50" s="4">
-        <v>86242.724574749998</v>
-      </c>
-      <c r="F50" s="3">
-        <v>2.8921735657111581E-3</v>
-      </c>
-      <c r="G50" s="3">
         <v>1.1051378185227779E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B52" s="6" t="s">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B51" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D52" s="4">
-        <f>AVERAGE(D47:D48)</f>
+      <c r="D51" s="4">
+        <f>AVERAGE(D46:D47)</f>
         <v>9545600.9495301731</v>
       </c>
-      <c r="E52" s="4">
-        <f t="shared" ref="E52:G52" si="8">AVERAGE(E47:E48)</f>
+      <c r="E51" s="4">
+        <f t="shared" ref="E51:G51" si="8">AVERAGE(E46:E47)</f>
         <v>148228.32764666999</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F51" s="3">
         <f t="shared" si="8"/>
         <v>2.6326858510279617E-3</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G51" s="3">
         <f t="shared" si="8"/>
         <v>1.5825783055181976E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B53" s="6" t="s">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B52" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="4">
-        <f>AVERAGE(D49:D50)</f>
+      <c r="D52" s="4">
+        <f>AVERAGE(D48:D49)</f>
         <v>8009823.6951486357</v>
       </c>
-      <c r="E53" s="4">
-        <f t="shared" ref="E53:G53" si="9">AVERAGE(E49:E50)</f>
+      <c r="E52" s="4">
+        <f t="shared" ref="E52:G52" si="9">AVERAGE(E48:E49)</f>
         <v>77995.203305984993</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F52" s="3">
         <f t="shared" si="9"/>
         <v>3.1436147390795297E-3</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G52" s="3">
         <f t="shared" si="9"/>
         <v>1.0372493950868561E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C55" s="6" t="s">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C54" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="4">
-        <f>D52/D53</f>
+      <c r="D54" s="4">
+        <f>D51/D52</f>
         <v>1.1917367114224651</v>
       </c>
-      <c r="E55" s="4">
-        <f t="shared" ref="E55:G55" si="10">E52/E53</f>
+      <c r="E54" s="4">
+        <f t="shared" ref="E54:G54" si="10">E51/E52</f>
         <v>1.9004800470248358</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F54" s="4">
         <f t="shared" si="10"/>
         <v>0.8374708956221617</v>
       </c>
-      <c r="G55" s="4">
+      <c r="G54" s="4">
         <f t="shared" si="10"/>
         <v>1.5257452190518532</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C57" s="2">
-        <f>MAX(C47:C50)</f>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C56" s="2">
+        <f>MAX(C46:C49)</f>
         <v>4</v>
       </c>
-      <c r="D57" s="2">
-        <f t="shared" ref="D57:G57" si="11">MAX(D47:D50)</f>
+      <c r="D56" s="2">
+        <f t="shared" ref="D56:G56" si="11">MAX(D46:D49)</f>
         <v>9937990.5894197039</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E56" s="2">
         <f t="shared" si="11"/>
         <v>158802.14720132999</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F56" s="2">
         <f t="shared" si="11"/>
         <v>3.3950559124479012E-3</v>
       </c>
-      <c r="G57" s="2">
+      <c r="G56" s="2">
         <f t="shared" si="11"/>
         <v>2.4032687441319662E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C58" s="7" t="s">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C57" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D57" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F57" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="G57" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J57" s="2"/>
+      <c r="K57" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C58" s="2">
+        <f>C46/C$56</f>
+        <v>0.5</v>
+      </c>
+      <c r="D58" s="2">
+        <f>D46/D$56</f>
+        <v>1</v>
+      </c>
+      <c r="E58" s="2">
+        <f>E46/E$56</f>
+        <v>0.86683026972860167</v>
+      </c>
+      <c r="F58" s="2">
+        <f>F46/F$56</f>
+        <v>0.72212245059815838</v>
+      </c>
+      <c r="G58" s="2">
+        <f>G46/G$56</f>
+        <v>0.31702150197089779</v>
+      </c>
+      <c r="J58" s="7">
+        <v>45</v>
+      </c>
+      <c r="K58" s="4">
+        <f>0.5*(D43*E43+E43*F43+F43*G43+G43*D43)</f>
+        <v>1.1693148402522289</v>
+      </c>
+      <c r="L58" s="4">
+        <f>0.5*(D40*E40+E40*F40+F40*G40+G40*D40)</f>
+        <v>0.44584555192110731</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C59" s="2">
-        <f>C47/C$57</f>
-        <v>0.5</v>
+        <f>C47/C$56</f>
+        <v>0.25</v>
       </c>
       <c r="D59" s="2">
-        <f t="shared" ref="D59:G59" si="12">D47/D$57</f>
+        <f>D47/D$56</f>
+        <v>0.9210323985801957</v>
+      </c>
+      <c r="E59" s="2">
+        <f>E47/E$56</f>
         <v>1</v>
       </c>
-      <c r="E59" s="2">
-        <f t="shared" si="12"/>
-        <v>0.86683026972860167</v>
-      </c>
       <c r="F59" s="2">
-        <f t="shared" si="12"/>
-        <v>0.72212245059815838</v>
+        <f>F47/F$56</f>
+        <v>0.82877150751032203</v>
       </c>
       <c r="G59" s="2">
-        <f t="shared" si="12"/>
-        <v>0.31702150197089779</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+        <f>G47/G$56</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C60" s="2">
-        <f t="shared" ref="C60:G62" si="13">C48/C$57</f>
-        <v>0.25</v>
+        <f>C48/C$56</f>
+        <v>0.75</v>
       </c>
       <c r="D60" s="2">
-        <f t="shared" si="13"/>
-        <v>0.9210323985801957</v>
+        <f>D48/D$56</f>
+        <v>0.83757880683679731</v>
       </c>
       <c r="E60" s="2">
-        <f t="shared" si="13"/>
+        <f>E48/E$56</f>
+        <v>0.43921120253363838</v>
+      </c>
+      <c r="F60" s="2">
+        <f>F48/F$56</f>
         <v>1</v>
       </c>
-      <c r="F60" s="2">
-        <f t="shared" si="13"/>
-        <v>0.82877150751032203</v>
-      </c>
       <c r="G60" s="2">
-        <f t="shared" si="13"/>
+        <f>G48/G$56</f>
+        <v>0.40335105011364702</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C61" s="2">
+        <f>C49/C$56</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C61" s="2">
-        <f t="shared" si="13"/>
-        <v>0.75</v>
-      </c>
       <c r="D61" s="2">
-        <f t="shared" si="13"/>
-        <v>0.83757880683679731</v>
+        <f>D49/D$56</f>
+        <v>0.77438160368646158</v>
       </c>
       <c r="E61" s="2">
-        <f t="shared" si="13"/>
-        <v>0.43921120253363838</v>
+        <f>E49/E$56</f>
+        <v>0.54308286187976496</v>
       </c>
       <c r="F61" s="2">
-        <f t="shared" si="13"/>
+        <f>F49/F$56</f>
+        <v>0.85187803685561247</v>
+      </c>
+      <c r="G61" s="2">
+        <f>G49/G$56</f>
+        <v>0.4598477890669449</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C63" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C64" s="4">
+        <v>0.77438160368646158</v>
+      </c>
+      <c r="D64" s="2">
         <v>1</v>
       </c>
-      <c r="G61" s="2">
-        <f t="shared" si="13"/>
-        <v>0.40335105011364702</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C62" s="2">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="D62" s="2">
-        <f t="shared" si="13"/>
-        <v>0.77438160368646158</v>
-      </c>
-      <c r="E62" s="2">
-        <f t="shared" si="13"/>
+      <c r="E64" s="2">
         <v>0.54308286187976496</v>
       </c>
-      <c r="F62" s="2">
-        <f t="shared" si="13"/>
+      <c r="F64" s="2">
         <v>0.85187803685561247</v>
       </c>
-      <c r="G62" s="2">
-        <f t="shared" si="13"/>
+      <c r="G64" s="2">
         <v>0.4598477890669449</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C64" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C65" s="4">
-        <v>0.77438160368646158</v>
+        <v>0.83757880683679731</v>
       </c>
       <c r="D65" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0.43921120253363838</v>
+      </c>
+      <c r="F65" s="2">
         <v>1</v>
       </c>
-      <c r="E65" s="2">
-        <v>0.54308286187976496</v>
-      </c>
-      <c r="F65" s="2">
-        <v>0.85187803685561247</v>
-      </c>
       <c r="G65" s="2">
-        <v>0.4598477890669449</v>
+        <v>0.40335105011364702</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C66" s="4">
-        <v>0.83757880683679731</v>
+        <v>0.9210323985801957</v>
       </c>
       <c r="D66" s="2">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="E66" s="2">
-        <v>0.43921120253363838</v>
+        <v>1</v>
       </c>
       <c r="F66" s="2">
+        <v>0.82877150751032203</v>
+      </c>
+      <c r="G66" s="2">
         <v>1</v>
-      </c>
-      <c r="G66" s="2">
-        <v>0.40335105011364702</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C67" s="4">
-        <v>0.9210323985801957</v>
+        <v>1</v>
       </c>
       <c r="D67" s="2">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E67" s="2">
+        <v>0.86683026972860167</v>
+      </c>
+      <c r="F67" s="2">
+        <v>0.72212245059815838</v>
+      </c>
+      <c r="G67" s="2">
+        <v>0.31702150197089779</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F67" s="2">
-        <v>0.82877150751032203</v>
-      </c>
-      <c r="G67" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C68" s="4">
-        <v>1</v>
-      </c>
-      <c r="D68" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E68" s="2">
-        <v>0.86683026972860167</v>
-      </c>
-      <c r="F68" s="2">
-        <v>0.72212245059815838</v>
-      </c>
-      <c r="G68" s="2">
-        <v>0.31702150197089779</v>
+      <c r="C69" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="2">
+        <v>4</v>
+      </c>
+      <c r="D70" s="4">
+        <v>5034263.5495518269</v>
+      </c>
+      <c r="E70" s="4">
+        <v>65873.429441999993</v>
+      </c>
+      <c r="F70" s="3">
+        <v>2.9423350149191101E-3</v>
+      </c>
+      <c r="G70" s="3">
+        <v>3.4897071466789652E-4</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D71" s="1" t="s">
+      <c r="A71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="2">
         <v>3</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>6</v>
+      <c r="D71" s="4">
+        <v>4961117.4365704898</v>
+      </c>
+      <c r="E71" s="4">
+        <v>63209.692581750001</v>
+      </c>
+      <c r="F71" s="3">
+        <v>4.351387458407175E-3</v>
+      </c>
+      <c r="G71" s="3">
+        <v>5.6592795928781631E-4</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -4714,19 +4737,19 @@
         <v>12</v>
       </c>
       <c r="C72" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D72" s="4">
-        <v>5034263.5495518269</v>
+        <v>4783385.1798815951</v>
       </c>
       <c r="E72" s="4">
-        <v>65873.429441999993</v>
+        <v>64669.840333150009</v>
       </c>
       <c r="F72" s="3">
-        <v>2.9423350149191101E-3</v>
+        <v>2.0954023999737231E-3</v>
       </c>
       <c r="G72" s="3">
-        <v>3.4897071466789652E-4</v>
+        <v>5.9056880507593645E-4</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -4737,344 +4760,353 @@
         <v>12</v>
       </c>
       <c r="C73" s="2">
+        <v>1</v>
+      </c>
+      <c r="D73" s="4">
+        <v>4448196.0441567702</v>
+      </c>
+      <c r="E73" s="4">
+        <v>96473.926682400008</v>
+      </c>
+      <c r="F73" s="3">
+        <v>4.425446074207404E-4</v>
+      </c>
+      <c r="G73" s="3">
+        <v>2.154034060250509E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B75" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="4">
+        <f>AVERAGE(D70:D71)</f>
+        <v>4997690.4930611588</v>
+      </c>
+      <c r="E75" s="4">
+        <f t="shared" ref="E75:G75" si="12">AVERAGE(E70:E71)</f>
+        <v>64541.561011874997</v>
+      </c>
+      <c r="F75" s="3">
+        <f t="shared" si="12"/>
+        <v>3.6468612366631426E-3</v>
+      </c>
+      <c r="G75" s="3">
+        <f t="shared" si="12"/>
+        <v>4.5744933697785639E-4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B76" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="4">
+        <f>AVERAGE(D72:D73)</f>
+        <v>4615790.6120191831</v>
+      </c>
+      <c r="E76" s="4">
+        <f t="shared" ref="E76:G76" si="13">AVERAGE(E72:E73)</f>
+        <v>80571.883507775012</v>
+      </c>
+      <c r="F76" s="3">
+        <f t="shared" si="13"/>
+        <v>1.2689735036972318E-3</v>
+      </c>
+      <c r="G76" s="3">
+        <f t="shared" si="13"/>
+        <v>4.0298610555049367E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C78" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78" s="4">
+        <f>D75/D76</f>
+        <v>1.0827376961267559</v>
+      </c>
+      <c r="E78" s="4">
+        <f t="shared" ref="E78:G78" si="14">E75/E76</f>
+        <v>0.80104322006630113</v>
+      </c>
+      <c r="F78" s="4">
+        <f t="shared" si="14"/>
+        <v>2.8738671264906555</v>
+      </c>
+      <c r="G78" s="4">
+        <f t="shared" si="14"/>
+        <v>1.1351491544676557</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C80" s="2">
+        <f>MAX(C70:C73)</f>
+        <v>4</v>
+      </c>
+      <c r="D80" s="2">
+        <f t="shared" ref="D80:G80" si="15">MAX(D70:D73)</f>
+        <v>5034263.5495518269</v>
+      </c>
+      <c r="E80" s="2">
+        <f t="shared" si="15"/>
+        <v>96473.926682400008</v>
+      </c>
+      <c r="F80" s="2">
+        <f t="shared" si="15"/>
+        <v>4.351387458407175E-3</v>
+      </c>
+      <c r="G80" s="2">
+        <f t="shared" si="15"/>
+        <v>5.9056880507593645E-4</v>
+      </c>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D81" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D73" s="4">
-        <v>4961117.4365704898</v>
-      </c>
-      <c r="E73" s="4">
-        <v>63209.692581750001</v>
-      </c>
-      <c r="F73" s="3">
-        <v>4.351387458407175E-3</v>
-      </c>
-      <c r="G73" s="3">
-        <v>5.6592795928781631E-4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C74" s="2">
-        <v>2</v>
-      </c>
-      <c r="D74" s="4">
-        <v>4783385.1798815951</v>
-      </c>
-      <c r="E74" s="4">
-        <v>64669.840333150009</v>
-      </c>
-      <c r="F74" s="3">
-        <v>2.0954023999737231E-3</v>
-      </c>
-      <c r="G74" s="3">
-        <v>5.9056880507593645E-4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C75" s="2">
+      <c r="E81" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J81" s="2"/>
+      <c r="K81" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L81" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C82" s="2">
+        <f>C70/C$80</f>
         <v>1</v>
       </c>
-      <c r="D75" s="4">
-        <v>4448196.0441567702</v>
-      </c>
-      <c r="E75" s="4">
-        <v>96473.926682400008</v>
-      </c>
-      <c r="F75" s="3">
-        <v>4.425446074207404E-4</v>
-      </c>
-      <c r="G75" s="3">
-        <v>2.154034060250509E-4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B77" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D77" s="4">
-        <f>AVERAGE(D72:D73)</f>
-        <v>4997690.4930611588</v>
-      </c>
-      <c r="E77" s="4">
-        <f t="shared" ref="E77:G77" si="14">AVERAGE(E72:E73)</f>
-        <v>64541.561011874997</v>
-      </c>
-      <c r="F77" s="3">
-        <f t="shared" si="14"/>
-        <v>3.6468612366631426E-3</v>
-      </c>
-      <c r="G77" s="3">
-        <f t="shared" si="14"/>
-        <v>4.5744933697785639E-4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B78" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D78" s="4">
-        <f>AVERAGE(D74:D75)</f>
-        <v>4615790.6120191831</v>
-      </c>
-      <c r="E78" s="4">
-        <f t="shared" ref="E78:G78" si="15">AVERAGE(E74:E75)</f>
-        <v>80571.883507775012</v>
-      </c>
-      <c r="F78" s="3">
-        <f t="shared" si="15"/>
-        <v>1.2689735036972318E-3</v>
-      </c>
-      <c r="G78" s="3">
-        <f t="shared" si="15"/>
-        <v>4.0298610555049367E-4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C80" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D80" s="4">
-        <f>D77/D78</f>
-        <v>1.0827376961267559</v>
-      </c>
-      <c r="E80" s="4">
-        <f t="shared" ref="E80:G80" si="16">E77/E78</f>
-        <v>0.80104322006630113</v>
-      </c>
-      <c r="F80" s="4">
-        <f t="shared" si="16"/>
-        <v>2.8738671264906555</v>
-      </c>
-      <c r="G80" s="4">
-        <f t="shared" si="16"/>
-        <v>1.1351491544676557</v>
-      </c>
-    </row>
-    <row r="82" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C82" s="2">
-        <f>MAX(C72:C75)</f>
+      <c r="D82" s="2">
+        <f>D70/D$80</f>
+        <v>1</v>
+      </c>
+      <c r="E82" s="2">
+        <f>E70/E$80</f>
+        <v>0.68281070033420188</v>
+      </c>
+      <c r="F82" s="2">
+        <f>F70/F$80</f>
+        <v>0.67618318135157551</v>
+      </c>
+      <c r="G82" s="2">
+        <f>G70/G$80</f>
+        <v>0.59090610893852613</v>
+      </c>
+      <c r="J82" s="7">
+        <v>46</v>
+      </c>
+      <c r="K82" s="4">
+        <f>0.5*(D67*E67+E67*F67+F67*G67+G67*D67)</f>
+        <v>0.72340591418718192</v>
+      </c>
+      <c r="L82" s="4">
+        <f>0.5*(D64*E64+E64*F64+F64*G64+G64*D64)</f>
+        <v>0.92865262248875724</v>
+      </c>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C83" s="2">
+        <f>C71/C$80</f>
+        <v>0.75</v>
+      </c>
+      <c r="D83" s="2">
+        <f>D71/D$80</f>
+        <v>0.98547034491512686</v>
+      </c>
+      <c r="E83" s="2">
+        <f>E71/E$80</f>
+        <v>0.65519974935654313</v>
+      </c>
+      <c r="F83" s="2">
+        <f>F71/F$80</f>
+        <v>1</v>
+      </c>
+      <c r="G83" s="2">
+        <f>G71/G$80</f>
+        <v>0.95827607964333339</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C84" s="2">
+        <f>C72/C$80</f>
+        <v>0.5</v>
+      </c>
+      <c r="D84" s="2">
+        <f>D72/D$80</f>
+        <v>0.95016582520941595</v>
+      </c>
+      <c r="E84" s="2">
+        <f>E72/E$80</f>
+        <v>0.67033490350245994</v>
+      </c>
+      <c r="F84" s="2">
+        <f>F72/F$80</f>
+        <v>0.48154810850623375</v>
+      </c>
+      <c r="G84" s="2">
+        <f>G72/G$80</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C85" s="2">
+        <f>C73/C$80</f>
+        <v>0.25</v>
+      </c>
+      <c r="D85" s="2">
+        <f>D73/D$80</f>
+        <v>0.88358426220112551</v>
+      </c>
+      <c r="E85" s="2">
+        <f>E73/E$80</f>
+        <v>1</v>
+      </c>
+      <c r="F85" s="2">
+        <f>F73/F$80</f>
+        <v>0.10170195406656198</v>
+      </c>
+      <c r="G85" s="2">
+        <f>G73/G$80</f>
+        <v>0.36473888253774922</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C87" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D82" s="2">
-        <f t="shared" ref="D82:G82" si="17">MAX(D72:D75)</f>
-        <v>5034263.5495518269</v>
-      </c>
-      <c r="E82" s="2">
-        <f t="shared" si="17"/>
-        <v>96473.926682400008</v>
-      </c>
-      <c r="F82" s="2">
-        <f t="shared" si="17"/>
-        <v>4.351387458407175E-3</v>
-      </c>
-      <c r="G82" s="2">
-        <f t="shared" si="17"/>
-        <v>5.9056880507593645E-4</v>
-      </c>
-    </row>
-    <row r="83" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C83" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F83" s="1" t="s">
+      <c r="F87" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G83" s="1" t="s">
+      <c r="G87" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C84" s="2">
-        <f>C72/C$82</f>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C88" s="4">
+        <v>0.88358426220112551</v>
+      </c>
+      <c r="D88" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E88" s="2">
         <v>1</v>
       </c>
-      <c r="D84" s="2">
-        <f t="shared" ref="D84:G84" si="18">D72/D$82</f>
+      <c r="F88" s="2">
+        <v>0.10170195406656198</v>
+      </c>
+      <c r="G88" s="2">
+        <v>0.36473888253774922</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C89" s="4">
+        <v>0.95016582520941595</v>
+      </c>
+      <c r="D89" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0.67033490350245994</v>
+      </c>
+      <c r="F89" s="2">
+        <v>0.48154810850623375</v>
+      </c>
+      <c r="G89" s="2">
         <v>1</v>
       </c>
-      <c r="E84" s="2">
-        <f t="shared" si="18"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C90" s="4">
+        <v>0.98547034491512686</v>
+      </c>
+      <c r="D90" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E90" s="2">
+        <v>0.65519974935654313</v>
+      </c>
+      <c r="F90" s="2">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2">
+        <v>0.95827607964333339</v>
+      </c>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C91" s="4">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2">
+        <v>1</v>
+      </c>
+      <c r="E91" s="2">
         <v>0.68281070033420188</v>
       </c>
-      <c r="F84" s="2">
-        <f t="shared" si="18"/>
+      <c r="F91" s="2">
         <v>0.67618318135157551</v>
       </c>
-      <c r="G84" s="2">
-        <f t="shared" si="18"/>
+      <c r="G91" s="2">
         <v>0.59090610893852613</v>
       </c>
     </row>
-    <row r="85" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C85" s="2">
-        <f t="shared" ref="C85:G87" si="19">C73/C$82</f>
-        <v>0.75</v>
-      </c>
-      <c r="D85" s="2">
-        <f t="shared" si="19"/>
-        <v>0.98547034491512686</v>
-      </c>
-      <c r="E85" s="2">
-        <f t="shared" si="19"/>
-        <v>0.65519974935654313</v>
-      </c>
-      <c r="F85" s="2">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G85" s="2">
-        <f t="shared" si="19"/>
-        <v>0.95827607964333339</v>
-      </c>
-    </row>
-    <row r="86" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C86" s="2">
-        <f t="shared" si="19"/>
-        <v>0.5</v>
-      </c>
-      <c r="D86" s="2">
-        <f t="shared" si="19"/>
-        <v>0.95016582520941595</v>
-      </c>
-      <c r="E86" s="2">
-        <f t="shared" si="19"/>
-        <v>0.67033490350245994</v>
-      </c>
-      <c r="F86" s="2">
-        <f t="shared" si="19"/>
-        <v>0.48154810850623375</v>
-      </c>
-      <c r="G86" s="2">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C87" s="2">
-        <f t="shared" si="19"/>
-        <v>0.25</v>
-      </c>
-      <c r="D87" s="2">
-        <f t="shared" si="19"/>
-        <v>0.88358426220112551</v>
-      </c>
-      <c r="E87" s="2">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="F87" s="2">
-        <f t="shared" si="19"/>
-        <v>0.10170195406656198</v>
-      </c>
-      <c r="G87" s="2">
-        <f t="shared" si="19"/>
-        <v>0.36473888253774922</v>
-      </c>
-    </row>
-    <row r="89" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C89" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="90" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C90" s="4">
-        <v>0.88358426220112551</v>
-      </c>
-      <c r="D90" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E90" s="2">
-        <v>1</v>
-      </c>
-      <c r="F90" s="2">
-        <v>0.10170195406656198</v>
-      </c>
-      <c r="G90" s="2">
-        <v>0.36473888253774922</v>
-      </c>
-    </row>
-    <row r="91" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C91" s="4">
-        <v>0.95016582520941595</v>
-      </c>
-      <c r="D91" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E91" s="2">
-        <v>0.67033490350245994</v>
-      </c>
-      <c r="F91" s="2">
-        <v>0.48154810850623375</v>
-      </c>
-      <c r="G91" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C92" s="4">
-        <v>0.98547034491512686</v>
-      </c>
-      <c r="D92" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E92" s="2">
-        <v>0.65519974935654313</v>
-      </c>
-      <c r="F92" s="2">
-        <v>1</v>
-      </c>
-      <c r="G92" s="2">
-        <v>0.95827607964333339</v>
-      </c>
-    </row>
-    <row r="93" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C93" s="4">
-        <v>1</v>
-      </c>
-      <c r="D93" s="2">
-        <v>1</v>
-      </c>
-      <c r="E93" s="2">
-        <v>0.68281070033420188</v>
-      </c>
-      <c r="F93" s="2">
-        <v>0.67618318135157551</v>
-      </c>
-      <c r="G93" s="2">
-        <v>0.59090610893852613</v>
-      </c>
+    <row r="105" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J105" s="2"/>
+      <c r="K105" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L105" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J106" s="7">
+        <v>47</v>
+      </c>
+      <c r="K106" s="4">
+        <f>0.5*(D91*E91+E91*F91+F91*G91+G91*D91)</f>
+        <v>1.0674913467538696</v>
+      </c>
+      <c r="L106" s="4">
+        <f>0.5*(D88*E88+E88*F88+F88*G88+G88*D88)</f>
+        <v>0.2399906658895713</v>
+      </c>
+    </row>
+    <row r="107" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J107" s="7"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+    </row>
+    <row r="108" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J108" s="2"/>
+      <c r="K108" s="7"/>
+      <c r="L108" s="7"/>
+    </row>
+    <row r="109" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J109" s="7"/>
+      <c r="K109" s="4"/>
+      <c r="L109" s="4"/>
     </row>
   </sheetData>
-  <sortState ref="C90:G93">
+  <sortState ref="C88:G91">
     <sortCondition ref="C90:C93"/>
   </sortState>
   <conditionalFormatting sqref="D2:D13">
@@ -5269,7 +5301,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D47:D50">
+  <conditionalFormatting sqref="D46:D49">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -5281,7 +5313,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E47:E50">
+  <conditionalFormatting sqref="E46:E49">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -5293,7 +5325,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F47:F50">
+  <conditionalFormatting sqref="F46:F49">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -5305,7 +5337,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G47:G50">
+  <conditionalFormatting sqref="G46:G49">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -5317,7 +5349,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D52:D53">
+  <conditionalFormatting sqref="D51:D52">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -5329,7 +5361,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E52:E53">
+  <conditionalFormatting sqref="E51:E52">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -5341,7 +5373,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F52:F53">
+  <conditionalFormatting sqref="F51:F52">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -5353,7 +5385,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G52:G53">
+  <conditionalFormatting sqref="G51:G52">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -5365,7 +5397,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D72:D75">
+  <conditionalFormatting sqref="D70:D73">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -5377,7 +5409,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E72:E75">
+  <conditionalFormatting sqref="E70:E73">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -5389,7 +5421,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F72:F75">
+  <conditionalFormatting sqref="F70:F73">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -5401,7 +5433,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G72:G75">
+  <conditionalFormatting sqref="G70:G73">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -5413,7 +5445,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D77:D78">
+  <conditionalFormatting sqref="D75:D76">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -5425,7 +5457,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E77:E78">
+  <conditionalFormatting sqref="E75:E76">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -5437,7 +5469,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F77:F78">
+  <conditionalFormatting sqref="F75:F76">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -5449,7 +5481,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G77:G78">
+  <conditionalFormatting sqref="G75:G76">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/clustering/sepsectors/retail sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/retail sector (VDS_s) 0.xlsx
@@ -4478,23 +4478,23 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C58" s="2">
-        <f>C46/C$56</f>
+        <f t="shared" ref="C58:G61" si="12">C46/C$56</f>
         <v>0.5</v>
       </c>
       <c r="D58" s="2">
-        <f>D46/D$56</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E58" s="2">
-        <f>E46/E$56</f>
+        <f t="shared" si="12"/>
         <v>0.86683026972860167</v>
       </c>
       <c r="F58" s="2">
-        <f>F46/F$56</f>
+        <f t="shared" si="12"/>
         <v>0.72212245059815838</v>
       </c>
       <c r="G58" s="2">
-        <f>G46/G$56</f>
+        <f t="shared" si="12"/>
         <v>0.31702150197089779</v>
       </c>
       <c r="J58" s="7">
@@ -4511,67 +4511,67 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C59" s="2">
-        <f>C47/C$56</f>
+        <f t="shared" si="12"/>
         <v>0.25</v>
       </c>
       <c r="D59" s="2">
-        <f>D47/D$56</f>
+        <f t="shared" si="12"/>
         <v>0.9210323985801957</v>
       </c>
       <c r="E59" s="2">
-        <f>E47/E$56</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="F59" s="2">
-        <f>F47/F$56</f>
+        <f t="shared" si="12"/>
         <v>0.82877150751032203</v>
       </c>
       <c r="G59" s="2">
-        <f>G47/G$56</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C60" s="2">
-        <f>C48/C$56</f>
+        <f t="shared" si="12"/>
         <v>0.75</v>
       </c>
       <c r="D60" s="2">
-        <f>D48/D$56</f>
+        <f t="shared" si="12"/>
         <v>0.83757880683679731</v>
       </c>
       <c r="E60" s="2">
-        <f>E48/E$56</f>
+        <f t="shared" si="12"/>
         <v>0.43921120253363838</v>
       </c>
       <c r="F60" s="2">
-        <f>F48/F$56</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G60" s="2">
-        <f>G48/G$56</f>
+        <f t="shared" si="12"/>
         <v>0.40335105011364702</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C61" s="2">
-        <f>C49/C$56</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="D61" s="2">
-        <f>D49/D$56</f>
+        <f t="shared" si="12"/>
         <v>0.77438160368646158</v>
       </c>
       <c r="E61" s="2">
-        <f>E49/E$56</f>
+        <f t="shared" si="12"/>
         <v>0.54308286187976496</v>
       </c>
       <c r="F61" s="2">
-        <f>F49/F$56</f>
+        <f t="shared" si="12"/>
         <v>0.85187803685561247</v>
       </c>
       <c r="G61" s="2">
-        <f>G49/G$56</f>
+        <f t="shared" si="12"/>
         <v>0.4598477890669449</v>
       </c>
     </row>
@@ -4784,15 +4784,15 @@
         <v>4997690.4930611588</v>
       </c>
       <c r="E75" s="4">
-        <f t="shared" ref="E75:G75" si="12">AVERAGE(E70:E71)</f>
+        <f t="shared" ref="E75:G75" si="13">AVERAGE(E70:E71)</f>
         <v>64541.561011874997</v>
       </c>
       <c r="F75" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.6468612366631426E-3</v>
       </c>
       <c r="G75" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.5744933697785639E-4</v>
       </c>
     </row>
@@ -4805,15 +4805,15 @@
         <v>4615790.6120191831</v>
       </c>
       <c r="E76" s="4">
-        <f t="shared" ref="E76:G76" si="13">AVERAGE(E72:E73)</f>
+        <f t="shared" ref="E76:G76" si="14">AVERAGE(E72:E73)</f>
         <v>80571.883507775012</v>
       </c>
       <c r="F76" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.2689735036972318E-3</v>
       </c>
       <c r="G76" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.0298610555049367E-4</v>
       </c>
     </row>
@@ -4826,15 +4826,15 @@
         <v>1.0827376961267559</v>
       </c>
       <c r="E78" s="4">
-        <f t="shared" ref="E78:G78" si="14">E75/E76</f>
+        <f t="shared" ref="E78:G78" si="15">E75/E76</f>
         <v>0.80104322006630113</v>
       </c>
       <c r="F78" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.8738671264906555</v>
       </c>
       <c r="G78" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.1351491544676557</v>
       </c>
     </row>
@@ -4844,19 +4844,19 @@
         <v>4</v>
       </c>
       <c r="D80" s="2">
-        <f t="shared" ref="D80:G80" si="15">MAX(D70:D73)</f>
+        <f t="shared" ref="D80:G80" si="16">MAX(D70:D73)</f>
         <v>5034263.5495518269</v>
       </c>
       <c r="E80" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>96473.926682400008</v>
       </c>
       <c r="F80" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.351387458407175E-3</v>
       </c>
       <c r="G80" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5.9056880507593645E-4</v>
       </c>
     </row>
@@ -4886,23 +4886,23 @@
     </row>
     <row r="82" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C82" s="2">
-        <f>C70/C$80</f>
+        <f t="shared" ref="C82:G85" si="17">C70/C$80</f>
         <v>1</v>
       </c>
       <c r="D82" s="2">
-        <f>D70/D$80</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="E82" s="2">
-        <f>E70/E$80</f>
+        <f t="shared" si="17"/>
         <v>0.68281070033420188</v>
       </c>
       <c r="F82" s="2">
-        <f>F70/F$80</f>
+        <f t="shared" si="17"/>
         <v>0.67618318135157551</v>
       </c>
       <c r="G82" s="2">
-        <f>G70/G$80</f>
+        <f t="shared" si="17"/>
         <v>0.59090610893852613</v>
       </c>
       <c r="J82" s="7">
@@ -4919,67 +4919,67 @@
     </row>
     <row r="83" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C83" s="2">
-        <f>C71/C$80</f>
+        <f t="shared" si="17"/>
         <v>0.75</v>
       </c>
       <c r="D83" s="2">
-        <f>D71/D$80</f>
+        <f t="shared" si="17"/>
         <v>0.98547034491512686</v>
       </c>
       <c r="E83" s="2">
-        <f>E71/E$80</f>
+        <f t="shared" si="17"/>
         <v>0.65519974935654313</v>
       </c>
       <c r="F83" s="2">
-        <f>F71/F$80</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G83" s="2">
-        <f>G71/G$80</f>
+        <f t="shared" si="17"/>
         <v>0.95827607964333339</v>
       </c>
     </row>
     <row r="84" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C84" s="2">
-        <f>C72/C$80</f>
+        <f t="shared" si="17"/>
         <v>0.5</v>
       </c>
       <c r="D84" s="2">
-        <f>D72/D$80</f>
+        <f t="shared" si="17"/>
         <v>0.95016582520941595</v>
       </c>
       <c r="E84" s="2">
-        <f>E72/E$80</f>
+        <f t="shared" si="17"/>
         <v>0.67033490350245994</v>
       </c>
       <c r="F84" s="2">
-        <f>F72/F$80</f>
+        <f t="shared" si="17"/>
         <v>0.48154810850623375</v>
       </c>
       <c r="G84" s="2">
-        <f>G72/G$80</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C85" s="2">
-        <f>C73/C$80</f>
+        <f t="shared" si="17"/>
         <v>0.25</v>
       </c>
       <c r="D85" s="2">
-        <f>D73/D$80</f>
+        <f t="shared" si="17"/>
         <v>0.88358426220112551</v>
       </c>
       <c r="E85" s="2">
-        <f>E73/E$80</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="F85" s="2">
-        <f>F73/F$80</f>
+        <f t="shared" si="17"/>
         <v>0.10170195406656198</v>
       </c>
       <c r="G85" s="2">
-        <f>G73/G$80</f>
+        <f t="shared" si="17"/>
         <v>0.36473888253774922</v>
       </c>
     </row>

--- a/clustering/sepsectors/retail sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/retail sector (VDS_s) 0.xlsx
@@ -9,17 +9,21 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="21">
   <si>
     <t>sector</t>
   </si>
@@ -1431,6 +1435,1197 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>45</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,85</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$40:$G$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.42536572944710072</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.12558758459002764</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2C8F-4029-98BE-98FB948B274B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$43</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$43:$G$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.50939923098586959</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.82696058644524917</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-2C8F-4029-98BE-98FB948B274B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="285497360"/>
+        <c:axId val="285495696"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="285497360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285495696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="285495696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285497360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>46</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$64</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,77</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$64:$G$64</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.54308286187976496</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.85187803685561247</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.4598477890669449</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E488-446A-A3CB-A5AE88A83FBC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$67</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$67:$G$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.86683026972860167</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.72212245059815838</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.31702150197089779</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-E488-446A-A3CB-A5AE88A83FBC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="285497360"/>
+        <c:axId val="285495696"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="285497360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285495696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="285495696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285497360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>47</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$88</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,88</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$88:$G$88</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.10170195406656198</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.36473888253774922</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8923-4DAD-A337-39FDFDAAD406}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$91</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$91:$G$91</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.68281070033420188</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.67618318135157551</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.59090610893852613</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-8923-4DAD-A337-39FDFDAAD406}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="285497360"/>
+        <c:axId val="285495696"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="285497360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285495696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="285495696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285497360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1551,6 +2746,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
@@ -2562,6 +3877,1521 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3165,6 +5995,190 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>207818</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>121227</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>152153</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>167987</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Диаграмма 4"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>380999</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>155864</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>325334</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>12124</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Диаграмма 5"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>242453</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>186788</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>46760</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Диаграмма 6"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet1 (2)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="42">
+          <cell r="E42" t="str">
+            <v>ITcosts_s</v>
+          </cell>
+          <cell r="F42" t="str">
+            <v>skvozcosts_s</v>
+          </cell>
+          <cell r="G42" t="str">
+            <v>trainingcosts_s</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="C43">
+            <v>0.53195397442833625</v>
+          </cell>
+          <cell r="E43">
+            <v>1</v>
+          </cell>
+          <cell r="F43">
+            <v>0.4341128768543896</v>
+          </cell>
+          <cell r="G43">
+            <v>0.96268324181002174</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="C44">
+            <v>0.74071957251902487</v>
+          </cell>
+          <cell r="E44">
+            <v>0.81436789578742097</v>
+          </cell>
+          <cell r="F44">
+            <v>1</v>
+          </cell>
+          <cell r="G44">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="C45">
+            <v>0.88899585107146872</v>
+          </cell>
+          <cell r="E45">
+            <v>0.3732928962109599</v>
+          </cell>
+          <cell r="F45">
+            <v>0.78623653793827153</v>
+          </cell>
+          <cell r="G45">
+            <v>0.50683853134311552</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="C46">
+            <v>1</v>
+          </cell>
+          <cell r="E46">
+            <v>0.37449706271284755</v>
+          </cell>
+          <cell r="F46">
+            <v>0.59247665944601891</v>
+          </cell>
+          <cell r="G46">
+            <v>0.50683853134311552</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5497,4 +8511,2050 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L109"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="93" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D2" s="4">
+        <v>9937990.5894197039</v>
+      </c>
+      <c r="E2" s="4">
+        <v>137654.50809200999</v>
+      </c>
+      <c r="F2" s="3">
+        <v>2.451646095414645E-3</v>
+      </c>
+      <c r="G2" s="3">
+        <v>7.6188786690442915E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D3" s="4">
+        <v>9153211.3096406423</v>
+      </c>
+      <c r="E3" s="4">
+        <v>158802.14720132999</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2.8137256066412789E-3</v>
+      </c>
+      <c r="G3" s="3">
+        <v>2.4032687441319662E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D4" s="4">
+        <v>8323850.3002414759</v>
+      </c>
+      <c r="E4" s="4">
+        <v>69747.682037220002</v>
+      </c>
+      <c r="F4" s="3">
+        <v>3.3950559124479012E-3</v>
+      </c>
+      <c r="G4" s="3">
+        <v>9.6936097165093425E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D5" s="4">
+        <v>7695797.0900557945</v>
+      </c>
+      <c r="E5" s="4">
+        <v>86242.724574749998</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2.8921735657111581E-3</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1.1051378185227779E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D6" s="4">
+        <v>5034263.5495518269</v>
+      </c>
+      <c r="E6" s="4">
+        <v>65873.429441999993</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2.9423350149191101E-3</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3.4897071466789652E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D7" s="4">
+        <v>4961117.4365704898</v>
+      </c>
+      <c r="E7" s="4">
+        <v>63209.692581750001</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4.351387458407175E-3</v>
+      </c>
+      <c r="G7" s="3">
+        <v>5.6592795928781631E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D8" s="4">
+        <v>4783385.1798815951</v>
+      </c>
+      <c r="E8" s="4">
+        <v>64669.840333150009</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2.0954023999737231E-3</v>
+      </c>
+      <c r="G8" s="3">
+        <v>5.9056880507593645E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D9" s="4">
+        <v>4448196.0441567702</v>
+      </c>
+      <c r="E9" s="4">
+        <v>96473.926682400008</v>
+      </c>
+      <c r="F9" s="3">
+        <v>4.425446074207404E-4</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2.154034060250509E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1252686.154182706</v>
+      </c>
+      <c r="E10" s="4">
+        <v>9796.3168782600005</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.13430184443805829</v>
+      </c>
+      <c r="G10" s="3">
+        <v>5.218380319387952E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1194490.274669243</v>
+      </c>
+      <c r="E11" s="4">
+        <v>19231.118310289999</v>
+      </c>
+      <c r="F11" s="3">
+        <v>5.2147019888250969E-3</v>
+      </c>
+      <c r="G11" s="3">
+        <v>4.9058279907476332E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1165717.934645507</v>
+      </c>
+      <c r="E12" s="4">
+        <v>8785.8682089999984</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.025148686019859E-2</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1.7444704536200269E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1063712.5319653209</v>
+      </c>
+      <c r="E13" s="4">
+        <v>8180.2586681400007</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1.6866644248961379E-2</v>
+      </c>
+      <c r="G13" s="3">
+        <v>6.3103132179727491E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="4">
+        <f>MEDIAN(D2:D13)</f>
+        <v>4872251.3082260424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="4">
+        <f>AVERAGE(D2:D7)</f>
+        <v>7517705.0459133228</v>
+      </c>
+      <c r="E17" s="4">
+        <f t="shared" ref="E17:G17" si="0">AVERAGE(E2:E7)</f>
+        <v>96921.697321510001</v>
+      </c>
+      <c r="F17" s="3">
+        <f t="shared" si="0"/>
+        <v>3.141053942256878E-3</v>
+      </c>
+      <c r="G17" s="3">
+        <f t="shared" si="0"/>
+        <v>1.0257590125276369E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="4">
+        <f>AVERAGE(D8:D13)</f>
+        <v>2318031.3532501906</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" ref="E18:G18" si="1">AVERAGE(E8:E13)</f>
+        <v>34522.888180206675</v>
+      </c>
+      <c r="F18" s="3">
+        <f t="shared" si="1"/>
+        <v>2.8195437423906299E-2</v>
+      </c>
+      <c r="G18" s="3">
+        <f t="shared" si="1"/>
+        <v>4.3731190154563726E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1252686.154182706</v>
+      </c>
+      <c r="E22" s="4">
+        <v>9796.3168782600005</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0.13430184443805829</v>
+      </c>
+      <c r="G22" s="3">
+        <v>5.218380319387952E-4</v>
+      </c>
+      <c r="I22" s="7">
+        <v>45</v>
+      </c>
+      <c r="J22" s="4">
+        <v>1.1693148402522289</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0.44584555192110731</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1194490.274669243</v>
+      </c>
+      <c r="E23" s="4">
+        <v>19231.118310289999</v>
+      </c>
+      <c r="F23" s="3">
+        <v>5.2147019888250969E-3</v>
+      </c>
+      <c r="G23" s="3">
+        <v>4.9058279907476332E-4</v>
+      </c>
+      <c r="I23" s="7">
+        <v>46</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0.72340591418718192</v>
+      </c>
+      <c r="K23" s="4">
+        <v>0.92865262248875724</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2">
+        <v>4</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1165717.934645507</v>
+      </c>
+      <c r="E24" s="4">
+        <v>8785.8682089999984</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1.025148686019859E-2</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1.7444704536200269E-4</v>
+      </c>
+      <c r="I24" s="7">
+        <v>47</v>
+      </c>
+      <c r="J24" s="4">
+        <v>1.0674913467538696</v>
+      </c>
+      <c r="K24" s="4">
+        <v>0.2399906658895713</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1063712.5319653209</v>
+      </c>
+      <c r="E25" s="4">
+        <v>8180.2586681400007</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1.6866644248961379E-2</v>
+      </c>
+      <c r="G25" s="3">
+        <v>6.3103132179727491E-4</v>
+      </c>
+      <c r="I25" s="6"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I26" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="8">
+        <f>AVERAGE(J22:J24)</f>
+        <v>0.98673736706442672</v>
+      </c>
+      <c r="K26" s="8">
+        <f>AVERAGE(K22:K24)</f>
+        <v>0.53816294676647869</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="4">
+        <f>AVERAGE(D22:D23)</f>
+        <v>1223588.2144259745</v>
+      </c>
+      <c r="E27" s="4">
+        <f t="shared" ref="E27:G27" si="2">AVERAGE(E22:E23)</f>
+        <v>14513.717594275</v>
+      </c>
+      <c r="F27" s="3">
+        <f t="shared" si="2"/>
+        <v>6.9758273213441691E-2</v>
+      </c>
+      <c r="G27" s="3">
+        <f t="shared" si="2"/>
+        <v>5.0621041550677926E-4</v>
+      </c>
+      <c r="I27" s="6"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="4">
+        <f>AVERAGE(D24:D25)</f>
+        <v>1114715.233305414</v>
+      </c>
+      <c r="E28" s="4">
+        <f t="shared" ref="E28:G28" si="3">AVERAGE(E24:E25)</f>
+        <v>8483.0634385699996</v>
+      </c>
+      <c r="F28" s="3">
+        <f t="shared" si="3"/>
+        <v>1.3559065554579985E-2</v>
+      </c>
+      <c r="G28" s="3">
+        <f t="shared" si="3"/>
+        <v>4.0273918357963879E-4</v>
+      </c>
+      <c r="I28" s="6"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="4">
+        <f>D27/D28</f>
+        <v>1.0976688735092679</v>
+      </c>
+      <c r="E30" s="4">
+        <f t="shared" ref="E30:G30" si="4">E27/E28</f>
+        <v>1.7109052289159346</v>
+      </c>
+      <c r="F30" s="4">
+        <f t="shared" si="4"/>
+        <v>5.1447699646144658</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" si="4"/>
+        <v>1.2569187110314528</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C32" s="2">
+        <f>MAX(C22:C25)</f>
+        <v>4</v>
+      </c>
+      <c r="D32" s="2">
+        <f t="shared" ref="D32:G32" si="5">MAX(D22:D25)</f>
+        <v>1252686.154182706</v>
+      </c>
+      <c r="E32" s="2">
+        <f t="shared" si="5"/>
+        <v>19231.118310289999</v>
+      </c>
+      <c r="F32" s="2">
+        <f t="shared" si="5"/>
+        <v>0.13430184443805829</v>
+      </c>
+      <c r="G32" s="2">
+        <f t="shared" si="5"/>
+        <v>6.3103132179727491E-4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C34" s="2">
+        <f>C22/C$32</f>
+        <v>0.75</v>
+      </c>
+      <c r="D34" s="2">
+        <f t="shared" ref="D34:G34" si="6">D22/D$32</f>
+        <v>1</v>
+      </c>
+      <c r="E34" s="2">
+        <f t="shared" si="6"/>
+        <v>0.50939923098586959</v>
+      </c>
+      <c r="F34" s="2">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="G34" s="2">
+        <f t="shared" si="6"/>
+        <v>0.82696058644524917</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C35" s="2">
+        <f t="shared" ref="C35:G37" si="7">C23/C$32</f>
+        <v>0.25</v>
+      </c>
+      <c r="D35" s="2">
+        <f t="shared" si="7"/>
+        <v>0.95354312864467483</v>
+      </c>
+      <c r="E35" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <f t="shared" si="7"/>
+        <v>3.882822317626608E-2</v>
+      </c>
+      <c r="G35" s="2">
+        <f t="shared" si="7"/>
+        <v>0.7774301878986094</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C36" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="D36" s="2">
+        <f t="shared" si="7"/>
+        <v>0.93057461420259735</v>
+      </c>
+      <c r="E36" s="2">
+        <f t="shared" si="7"/>
+        <v>0.45685685394067499</v>
+      </c>
+      <c r="F36" s="2">
+        <f t="shared" si="7"/>
+        <v>7.6331690775302094E-2</v>
+      </c>
+      <c r="G36" s="2">
+        <f t="shared" si="7"/>
+        <v>0.27644752223257396</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.5</v>
+      </c>
+      <c r="D37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.84914527746123469</v>
+      </c>
+      <c r="E37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.42536572944710072</v>
+      </c>
+      <c r="F37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.12558758459002764</v>
+      </c>
+      <c r="G37" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C39" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C40" s="4">
+        <v>0.84914527746123469</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.42536572944710072</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0.12558758459002764</v>
+      </c>
+      <c r="G40" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C41" s="4">
+        <v>0.93057461420259735</v>
+      </c>
+      <c r="D41" s="2">
+        <v>1</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.45685685394067499</v>
+      </c>
+      <c r="F41" s="2">
+        <v>7.6331690775302094E-2</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0.27644752223257396</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C42" s="4">
+        <v>0.95354312864467483</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E42" s="2">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>3.882822317626608E-2</v>
+      </c>
+      <c r="G42" s="2">
+        <v>0.7774301878986094</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C43" s="4">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0.50939923098586959</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.82696058644524917</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="2">
+        <v>2</v>
+      </c>
+      <c r="D46" s="4">
+        <v>9937990.5894197039</v>
+      </c>
+      <c r="E46" s="4">
+        <v>137654.50809200999</v>
+      </c>
+      <c r="F46" s="3">
+        <v>2.451646095414645E-3</v>
+      </c>
+      <c r="G46" s="3">
+        <v>7.6188786690442915E-4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+      <c r="D47" s="4">
+        <v>9153211.3096406423</v>
+      </c>
+      <c r="E47" s="4">
+        <v>158802.14720132999</v>
+      </c>
+      <c r="F47" s="3">
+        <v>2.8137256066412789E-3</v>
+      </c>
+      <c r="G47" s="3">
+        <v>2.4032687441319662E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="2">
+        <v>3</v>
+      </c>
+      <c r="D48" s="4">
+        <v>8323850.3002414759</v>
+      </c>
+      <c r="E48" s="4">
+        <v>69747.682037220002</v>
+      </c>
+      <c r="F48" s="3">
+        <v>3.3950559124479012E-3</v>
+      </c>
+      <c r="G48" s="3">
+        <v>9.6936097165093425E-4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="2">
+        <v>4</v>
+      </c>
+      <c r="D49" s="4">
+        <v>7695797.0900557945</v>
+      </c>
+      <c r="E49" s="4">
+        <v>86242.724574749998</v>
+      </c>
+      <c r="F49" s="3">
+        <v>2.8921735657111581E-3</v>
+      </c>
+      <c r="G49" s="3">
+        <v>1.1051378185227779E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B51" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="4">
+        <f>AVERAGE(D46:D47)</f>
+        <v>9545600.9495301731</v>
+      </c>
+      <c r="E51" s="4">
+        <f t="shared" ref="E51:G51" si="8">AVERAGE(E46:E47)</f>
+        <v>148228.32764666999</v>
+      </c>
+      <c r="F51" s="3">
+        <f t="shared" si="8"/>
+        <v>2.6326858510279617E-3</v>
+      </c>
+      <c r="G51" s="3">
+        <f t="shared" si="8"/>
+        <v>1.5825783055181976E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B52" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="4">
+        <f>AVERAGE(D48:D49)</f>
+        <v>8009823.6951486357</v>
+      </c>
+      <c r="E52" s="4">
+        <f t="shared" ref="E52:G52" si="9">AVERAGE(E48:E49)</f>
+        <v>77995.203305984993</v>
+      </c>
+      <c r="F52" s="3">
+        <f t="shared" si="9"/>
+        <v>3.1436147390795297E-3</v>
+      </c>
+      <c r="G52" s="3">
+        <f t="shared" si="9"/>
+        <v>1.0372493950868561E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C54" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" s="4">
+        <f>D51/D52</f>
+        <v>1.1917367114224651</v>
+      </c>
+      <c r="E54" s="4">
+        <f t="shared" ref="E54:G54" si="10">E51/E52</f>
+        <v>1.9004800470248358</v>
+      </c>
+      <c r="F54" s="4">
+        <f t="shared" si="10"/>
+        <v>0.8374708956221617</v>
+      </c>
+      <c r="G54" s="4">
+        <f t="shared" si="10"/>
+        <v>1.5257452190518532</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C56" s="2">
+        <f>MAX(C46:C49)</f>
+        <v>4</v>
+      </c>
+      <c r="D56" s="2">
+        <f t="shared" ref="D56:G56" si="11">MAX(D46:D49)</f>
+        <v>9937990.5894197039</v>
+      </c>
+      <c r="E56" s="2">
+        <f t="shared" si="11"/>
+        <v>158802.14720132999</v>
+      </c>
+      <c r="F56" s="2">
+        <f t="shared" si="11"/>
+        <v>3.3950559124479012E-3</v>
+      </c>
+      <c r="G56" s="2">
+        <f t="shared" si="11"/>
+        <v>2.4032687441319662E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C57" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J57" s="2"/>
+      <c r="K57" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C58" s="2">
+        <f t="shared" ref="C58:G61" si="12">C46/C$56</f>
+        <v>0.5</v>
+      </c>
+      <c r="D58" s="2">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="E58" s="2">
+        <f t="shared" si="12"/>
+        <v>0.86683026972860167</v>
+      </c>
+      <c r="F58" s="2">
+        <f t="shared" si="12"/>
+        <v>0.72212245059815838</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="12"/>
+        <v>0.31702150197089779</v>
+      </c>
+      <c r="J58" s="7">
+        <v>45</v>
+      </c>
+      <c r="K58" s="4">
+        <f>0.5*(D43*E43+E43*F43+F43*G43+G43*D43)</f>
+        <v>1.1693148402522289</v>
+      </c>
+      <c r="L58" s="4">
+        <f>0.5*(D40*E40+E40*F40+F40*G40+G40*D40)</f>
+        <v>0.44584555192110731</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C59" s="2">
+        <f t="shared" si="12"/>
+        <v>0.25</v>
+      </c>
+      <c r="D59" s="2">
+        <f t="shared" si="12"/>
+        <v>0.9210323985801957</v>
+      </c>
+      <c r="E59" s="2">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="F59" s="2">
+        <f t="shared" si="12"/>
+        <v>0.82877150751032203</v>
+      </c>
+      <c r="G59" s="2">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C60" s="2">
+        <f t="shared" si="12"/>
+        <v>0.75</v>
+      </c>
+      <c r="D60" s="2">
+        <f t="shared" si="12"/>
+        <v>0.83757880683679731</v>
+      </c>
+      <c r="E60" s="2">
+        <f t="shared" si="12"/>
+        <v>0.43921120253363838</v>
+      </c>
+      <c r="F60" s="2">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="G60" s="2">
+        <f t="shared" si="12"/>
+        <v>0.40335105011364702</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C61" s="2">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="D61" s="2">
+        <f t="shared" si="12"/>
+        <v>0.77438160368646158</v>
+      </c>
+      <c r="E61" s="2">
+        <f t="shared" si="12"/>
+        <v>0.54308286187976496</v>
+      </c>
+      <c r="F61" s="2">
+        <f t="shared" si="12"/>
+        <v>0.85187803685561247</v>
+      </c>
+      <c r="G61" s="2">
+        <f t="shared" si="12"/>
+        <v>0.4598477890669449</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C63" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C64" s="4">
+        <v>0.77438160368646158</v>
+      </c>
+      <c r="D64" s="2">
+        <v>1</v>
+      </c>
+      <c r="E64" s="2">
+        <v>0.54308286187976496</v>
+      </c>
+      <c r="F64" s="2">
+        <v>0.85187803685561247</v>
+      </c>
+      <c r="G64" s="2">
+        <v>0.4598477890669449</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C65" s="4">
+        <v>0.83757880683679731</v>
+      </c>
+      <c r="D65" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0.43921120253363838</v>
+      </c>
+      <c r="F65" s="2">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2">
+        <v>0.40335105011364702</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C66" s="4">
+        <v>0.9210323985801957</v>
+      </c>
+      <c r="D66" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E66" s="2">
+        <v>1</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0.82877150751032203</v>
+      </c>
+      <c r="G66" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C67" s="4">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0.86683026972860167</v>
+      </c>
+      <c r="F67" s="2">
+        <v>0.72212245059815838</v>
+      </c>
+      <c r="G67" s="2">
+        <v>0.31702150197089779</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="2">
+        <v>4</v>
+      </c>
+      <c r="D70" s="4">
+        <v>5034263.5495518269</v>
+      </c>
+      <c r="E70" s="4">
+        <v>65873.429441999993</v>
+      </c>
+      <c r="F70" s="3">
+        <v>2.9423350149191101E-3</v>
+      </c>
+      <c r="G70" s="3">
+        <v>3.4897071466789652E-4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="2">
+        <v>3</v>
+      </c>
+      <c r="D71" s="4">
+        <v>4961117.4365704898</v>
+      </c>
+      <c r="E71" s="4">
+        <v>63209.692581750001</v>
+      </c>
+      <c r="F71" s="3">
+        <v>4.351387458407175E-3</v>
+      </c>
+      <c r="G71" s="3">
+        <v>5.6592795928781631E-4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="2">
+        <v>2</v>
+      </c>
+      <c r="D72" s="4">
+        <v>4783385.1798815951</v>
+      </c>
+      <c r="E72" s="4">
+        <v>64669.840333150009</v>
+      </c>
+      <c r="F72" s="3">
+        <v>2.0954023999737231E-3</v>
+      </c>
+      <c r="G72" s="3">
+        <v>5.9056880507593645E-4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="2">
+        <v>1</v>
+      </c>
+      <c r="D73" s="4">
+        <v>4448196.0441567702</v>
+      </c>
+      <c r="E73" s="4">
+        <v>96473.926682400008</v>
+      </c>
+      <c r="F73" s="3">
+        <v>4.425446074207404E-4</v>
+      </c>
+      <c r="G73" s="3">
+        <v>2.154034060250509E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B75" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="4">
+        <f>AVERAGE(D70:D71)</f>
+        <v>4997690.4930611588</v>
+      </c>
+      <c r="E75" s="4">
+        <f t="shared" ref="E75:G75" si="13">AVERAGE(E70:E71)</f>
+        <v>64541.561011874997</v>
+      </c>
+      <c r="F75" s="3">
+        <f t="shared" si="13"/>
+        <v>3.6468612366631426E-3</v>
+      </c>
+      <c r="G75" s="3">
+        <f t="shared" si="13"/>
+        <v>4.5744933697785639E-4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B76" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="4">
+        <f>AVERAGE(D72:D73)</f>
+        <v>4615790.6120191831</v>
+      </c>
+      <c r="E76" s="4">
+        <f t="shared" ref="E76:G76" si="14">AVERAGE(E72:E73)</f>
+        <v>80571.883507775012</v>
+      </c>
+      <c r="F76" s="3">
+        <f t="shared" si="14"/>
+        <v>1.2689735036972318E-3</v>
+      </c>
+      <c r="G76" s="3">
+        <f t="shared" si="14"/>
+        <v>4.0298610555049367E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C78" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78" s="4">
+        <f>D75/D76</f>
+        <v>1.0827376961267559</v>
+      </c>
+      <c r="E78" s="4">
+        <f t="shared" ref="E78:G78" si="15">E75/E76</f>
+        <v>0.80104322006630113</v>
+      </c>
+      <c r="F78" s="4">
+        <f t="shared" si="15"/>
+        <v>2.8738671264906555</v>
+      </c>
+      <c r="G78" s="4">
+        <f t="shared" si="15"/>
+        <v>1.1351491544676557</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C80" s="2">
+        <f>MAX(C70:C73)</f>
+        <v>4</v>
+      </c>
+      <c r="D80" s="2">
+        <f t="shared" ref="D80:G80" si="16">MAX(D70:D73)</f>
+        <v>5034263.5495518269</v>
+      </c>
+      <c r="E80" s="2">
+        <f t="shared" si="16"/>
+        <v>96473.926682400008</v>
+      </c>
+      <c r="F80" s="2">
+        <f t="shared" si="16"/>
+        <v>4.351387458407175E-3</v>
+      </c>
+      <c r="G80" s="2">
+        <f t="shared" si="16"/>
+        <v>5.9056880507593645E-4</v>
+      </c>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J81" s="2"/>
+      <c r="K81" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L81" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C82" s="2">
+        <f t="shared" ref="C82:G85" si="17">C70/C$80</f>
+        <v>1</v>
+      </c>
+      <c r="D82" s="2">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="E82" s="2">
+        <f t="shared" si="17"/>
+        <v>0.68281070033420188</v>
+      </c>
+      <c r="F82" s="2">
+        <f t="shared" si="17"/>
+        <v>0.67618318135157551</v>
+      </c>
+      <c r="G82" s="2">
+        <f t="shared" si="17"/>
+        <v>0.59090610893852613</v>
+      </c>
+      <c r="J82" s="7">
+        <v>46</v>
+      </c>
+      <c r="K82" s="4">
+        <f>0.5*(D67*E67+E67*F67+F67*G67+G67*D67)</f>
+        <v>0.72340591418718192</v>
+      </c>
+      <c r="L82" s="4">
+        <f>0.5*(D64*E64+E64*F64+F64*G64+G64*D64)</f>
+        <v>0.92865262248875724</v>
+      </c>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C83" s="2">
+        <f t="shared" si="17"/>
+        <v>0.75</v>
+      </c>
+      <c r="D83" s="2">
+        <f t="shared" si="17"/>
+        <v>0.98547034491512686</v>
+      </c>
+      <c r="E83" s="2">
+        <f t="shared" si="17"/>
+        <v>0.65519974935654313</v>
+      </c>
+      <c r="F83" s="2">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="G83" s="2">
+        <f t="shared" si="17"/>
+        <v>0.95827607964333339</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C84" s="2">
+        <f t="shared" si="17"/>
+        <v>0.5</v>
+      </c>
+      <c r="D84" s="2">
+        <f t="shared" si="17"/>
+        <v>0.95016582520941595</v>
+      </c>
+      <c r="E84" s="2">
+        <f t="shared" si="17"/>
+        <v>0.67033490350245994</v>
+      </c>
+      <c r="F84" s="2">
+        <f t="shared" si="17"/>
+        <v>0.48154810850623375</v>
+      </c>
+      <c r="G84" s="2">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C85" s="2">
+        <f t="shared" si="17"/>
+        <v>0.25</v>
+      </c>
+      <c r="D85" s="2">
+        <f t="shared" si="17"/>
+        <v>0.88358426220112551</v>
+      </c>
+      <c r="E85" s="2">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="F85" s="2">
+        <f t="shared" si="17"/>
+        <v>0.10170195406656198</v>
+      </c>
+      <c r="G85" s="2">
+        <f t="shared" si="17"/>
+        <v>0.36473888253774922</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C87" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C88" s="4">
+        <v>0.88358426220112551</v>
+      </c>
+      <c r="D88" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E88" s="2">
+        <v>1</v>
+      </c>
+      <c r="F88" s="2">
+        <v>0.10170195406656198</v>
+      </c>
+      <c r="G88" s="2">
+        <v>0.36473888253774922</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C89" s="4">
+        <v>0.95016582520941595</v>
+      </c>
+      <c r="D89" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0.67033490350245994</v>
+      </c>
+      <c r="F89" s="2">
+        <v>0.48154810850623375</v>
+      </c>
+      <c r="G89" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C90" s="4">
+        <v>0.98547034491512686</v>
+      </c>
+      <c r="D90" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E90" s="2">
+        <v>0.65519974935654313</v>
+      </c>
+      <c r="F90" s="2">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2">
+        <v>0.95827607964333339</v>
+      </c>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C91" s="4">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2">
+        <v>1</v>
+      </c>
+      <c r="E91" s="2">
+        <v>0.68281070033420188</v>
+      </c>
+      <c r="F91" s="2">
+        <v>0.67618318135157551</v>
+      </c>
+      <c r="G91" s="2">
+        <v>0.59090610893852613</v>
+      </c>
+    </row>
+    <row r="105" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J105" s="2"/>
+      <c r="K105" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L105" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J106" s="7">
+        <v>47</v>
+      </c>
+      <c r="K106" s="4">
+        <f>0.5*(D91*E91+E91*F91+F91*G91+G91*D91)</f>
+        <v>1.0674913467538696</v>
+      </c>
+      <c r="L106" s="4">
+        <f>0.5*(D88*E88+E88*F88+F88*G88+G88*D88)</f>
+        <v>0.2399906658895713</v>
+      </c>
+    </row>
+    <row r="107" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J107" s="7"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+    </row>
+    <row r="108" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J108" s="2"/>
+      <c r="K108" s="7"/>
+      <c r="L108" s="7"/>
+    </row>
+    <row r="109" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J109" s="7"/>
+      <c r="K109" s="4"/>
+      <c r="L109" s="4"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D13">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E13">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F13">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D18">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E18">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F18">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17:G18">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:D25">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E22:E25">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F25">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:G25">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D27:D28">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E27:E28">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27:F28">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27:G28">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D46:D49">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E46:E49">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F46:F49">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G46:G49">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D51:D52">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E51:E52">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F51:F52">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G51:G52">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D70:D73">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E70:E73">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F70:F73">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G70:G73">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D75:D76">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E75:E76">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F75:F76">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G75:G76">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>